--- a/Grade2-Homeworks.xlsx
+++ b/Grade2-Homeworks.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="136">
   <si>
     <t>Date</t>
   </si>
@@ -483,6 +483,41 @@
   </si>
   <si>
     <t>Check remaining AI exercises &amp; remaining HWs from 05 Dec 25</t>
+  </si>
+  <si>
+    <t>HW: Embed images into html: (1) Image from local folder
+Image in Base64 format (see example) - edit some of those values and see what happens.
+Create a long binary string and convert to hexadecimal, and Base64 (use 0-9, A-Z, a-z, + / symbols).
+Example: $1011_2 = (8+0+2+1){10} = {11}{10} = B_{16}$. (Binary, Decimal, Base16/Hexadecimal).</t>
+  </si>
+  <si>
+    <t>Complete copy tracing books (Latex) for English cursive, Telugu, Hindi.</t>
+  </si>
+  <si>
+    <t>Create Table of Contents (TOC) in a Markdown file for every subject in Grade 1 and Grade 2 - with links to all the files (use your updated TOC).
+Add to the 'Readme file' in 'Class Material' links &amp; description to Sahaja Yoga meditation &amp; your presentation video, ppt etc.
+Take your parents' help</t>
+  </si>
+  <si>
+    <t>HW: Complete all previous HWs</t>
+  </si>
+  <si>
+    <t>Record audio with both people singing and playing instruments for the following songs:
+Mata Nirmala Maheswari
+Raag Bilawal - Jaag Uthe Song
+Raag Jayjaywanti (flute) - Sharanu Gori Song</t>
+  </si>
+  <si>
+    <t>HW: For Jaag Uthe Song:
+Write it manually by hand
+Type it into the word document
+Memorize the meanings</t>
+  </si>
+  <si>
+    <t>Ayi Ayi Diwali Song - AI Breakdown
+HW: Fix AI breakdown - formatting and meanings
+HW: Write it manually - neatly!
+HW: Learn the meanings.</t>
   </si>
   <si>
     <t>Monday</t>
@@ -827,10 +862,10 @@
     <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -869,8 +904,8 @@
     <xf borderId="8" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="5" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2043,7 +2078,7 @@
         <v>45728.0</v>
       </c>
       <c r="B27" s="11"/>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="13" t="s">
         <v>53</v>
       </c>
       <c r="D27" s="11"/>
@@ -2082,7 +2117,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="27"/>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="28" t="s">
         <v>55</v>
       </c>
       <c r="F28" s="9"/>
@@ -2962,7 +2997,7 @@
       <c r="F55" s="9"/>
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
-      <c r="I55" s="40" t="s">
+      <c r="I55" s="39" t="s">
         <v>89</v>
       </c>
       <c r="O55" s="22"/>
@@ -2988,7 +3023,7 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="27"/>
-      <c r="D56" s="39" t="s">
+      <c r="D56" s="40" t="s">
         <v>90</v>
       </c>
       <c r="F56" s="9"/>
@@ -3626,23 +3661,25 @@
       <c r="AH73" s="9"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="53">
+      <c r="A74" s="47">
         <v>46065.0</v>
       </c>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="9"/>
-      <c r="J74" s="9"/>
-      <c r="K74" s="9"/>
-      <c r="L74" s="9"/>
-      <c r="M74" s="9"/>
-      <c r="N74" s="9"/>
-      <c r="O74" s="9"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="K74" s="11"/>
+      <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
+      <c r="N74" s="11"/>
+      <c r="O74" s="14"/>
       <c r="P74" s="9"/>
       <c r="Q74" s="4"/>
       <c r="R74" s="9"/>
@@ -3664,21 +3701,11 @@
       <c r="AH74" s="9"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="54"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="9"/>
-      <c r="J75" s="9"/>
-      <c r="K75" s="9"/>
-      <c r="L75" s="9"/>
-      <c r="M75" s="9"/>
-      <c r="N75" s="9"/>
-      <c r="O75" s="9"/>
+      <c r="A75" s="27"/>
+      <c r="J75" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="O75" s="22"/>
       <c r="P75" s="9"/>
       <c r="Q75" s="4"/>
       <c r="R75" s="9"/>
@@ -3700,21 +3727,23 @@
       <c r="AH75" s="9"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="54"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="9"/>
-      <c r="J76" s="9"/>
-      <c r="K76" s="9"/>
-      <c r="L76" s="9"/>
-      <c r="M76" s="9"/>
-      <c r="N76" s="9"/>
-      <c r="O76" s="9"/>
+      <c r="A76" s="29"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16"/>
+      <c r="H76" s="16"/>
+      <c r="I76" s="16"/>
+      <c r="J76" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="K76" s="16"/>
+      <c r="L76" s="16"/>
+      <c r="M76" s="16"/>
+      <c r="N76" s="16"/>
+      <c r="O76" s="18"/>
       <c r="P76" s="9"/>
       <c r="Q76" s="4"/>
       <c r="R76" s="9"/>
@@ -3736,21 +3765,27 @@
       <c r="AH76" s="9"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="54"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="9"/>
-      <c r="J77" s="9"/>
-      <c r="K77" s="9"/>
-      <c r="L77" s="9"/>
-      <c r="M77" s="9"/>
-      <c r="N77" s="9"/>
-      <c r="O77" s="9"/>
+      <c r="A77" s="47">
+        <v>46066.0</v>
+      </c>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="M77" s="11"/>
+      <c r="N77" s="11"/>
+      <c r="O77" s="14"/>
       <c r="P77" s="9"/>
       <c r="Q77" s="4"/>
       <c r="R77" s="9"/>
@@ -3772,21 +3807,14 @@
       <c r="AH77" s="9"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="54"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
+      <c r="A78" s="27"/>
+      <c r="E78" s="49" t="s">
+        <v>120</v>
+      </c>
       <c r="F78" s="9"/>
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
-      <c r="I78" s="9"/>
-      <c r="J78" s="9"/>
-      <c r="K78" s="9"/>
-      <c r="L78" s="9"/>
-      <c r="M78" s="9"/>
-      <c r="N78" s="9"/>
-      <c r="O78" s="9"/>
+      <c r="O78" s="22"/>
       <c r="P78" s="9"/>
       <c r="Q78" s="4"/>
       <c r="R78" s="9"/>
@@ -3808,21 +3836,23 @@
       <c r="AH78" s="9"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="54"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="9"/>
-      <c r="J79" s="9"/>
-      <c r="K79" s="9"/>
-      <c r="L79" s="9"/>
-      <c r="M79" s="9"/>
-      <c r="N79" s="9"/>
-      <c r="O79" s="9"/>
+      <c r="A79" s="29"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="F79" s="25"/>
+      <c r="G79" s="25"/>
+      <c r="H79" s="25"/>
+      <c r="I79" s="16"/>
+      <c r="J79" s="16"/>
+      <c r="K79" s="16"/>
+      <c r="L79" s="16"/>
+      <c r="M79" s="16"/>
+      <c r="N79" s="16"/>
+      <c r="O79" s="18"/>
       <c r="P79" s="9"/>
       <c r="Q79" s="4"/>
       <c r="R79" s="9"/>
@@ -11206,7 +11236,7 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="249">
+  <mergeCells count="274">
     <mergeCell ref="H22:H26"/>
     <mergeCell ref="I22:I26"/>
     <mergeCell ref="J22:J26"/>
@@ -11319,6 +11349,31 @@
     <mergeCell ref="E71:E73"/>
     <mergeCell ref="F71:F73"/>
     <mergeCell ref="G71:G73"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="I74:I76"/>
+    <mergeCell ref="K74:K76"/>
+    <mergeCell ref="L74:L76"/>
+    <mergeCell ref="M74:M76"/>
+    <mergeCell ref="N74:N76"/>
+    <mergeCell ref="O74:O76"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="B74:B76"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="D74:D76"/>
+    <mergeCell ref="E74:E76"/>
+    <mergeCell ref="F74:F76"/>
+    <mergeCell ref="G74:G76"/>
+    <mergeCell ref="L77:L79"/>
+    <mergeCell ref="M77:M79"/>
+    <mergeCell ref="N77:N79"/>
+    <mergeCell ref="O77:O79"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="D77:D79"/>
+    <mergeCell ref="I77:I79"/>
+    <mergeCell ref="J77:J79"/>
+    <mergeCell ref="K77:K79"/>
     <mergeCell ref="A54:A57"/>
     <mergeCell ref="A58:A59"/>
     <mergeCell ref="B58:B59"/>
@@ -11480,57 +11535,57 @@
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="55" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B2" s="55" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C2" s="55" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="55" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="55" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B4" s="55" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="55" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="55" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>

--- a/Grade2-Homeworks.xlsx
+++ b/Grade2-Homeworks.xlsx
@@ -10,14 +10,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="LEyUVtyEjz7mA1eI3CV7A9Y+kdDzzyKL8oajPvKJHyg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="0xw98/zXKwf9+k3L8Lti0SRu4PACmdSpzLy6n2QnbO0="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="148">
   <si>
     <t>Date</t>
   </si>
@@ -518,6 +518,45 @@
 HW: Fix AI breakdown - formatting and meanings
 HW: Write it manually - neatly!
 HW: Learn the meanings.</t>
+  </si>
+  <si>
+    <t>HW: Memorize last two stories by heart; Recite to your parents 10 times</t>
+  </si>
+  <si>
+    <t>HW: Complete textbook/workbook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latex copy tracing book - Telugu 
+ - HW: Verify and complete this </t>
+  </si>
+  <si>
+    <t>Prime factorization to find no. of common factors - See AI notes 
+     - HW: Complete AI exercises</t>
+  </si>
+  <si>
+    <t>Percentages, ratios, proportions (direct/indirect) - see AI notes
+     - HW: Complete AI exercises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HW: Complete (1) AP textbook </t>
+  </si>
+  <si>
+    <t>HW: Practice Ex-12 - write all of it yourself using functions from Ex-1 to 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2) Ap workbook </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3) Copy tracing book </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4) Copy tracing cursive </t>
+  </si>
+  <si>
+    <t>HW: Update Jupyter notebooks from 05 Dec 25</t>
+  </si>
+  <si>
+    <t>HW Read Ch.3 - AI Summary (Mahavira)</t>
   </si>
   <si>
     <t>Monday</t>
@@ -762,7 +801,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="60">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -905,6 +944,18 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -3874,21 +3925,25 @@
       <c r="AH79" s="9"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="54"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="9"/>
-      <c r="J80" s="9"/>
-      <c r="K80" s="9"/>
-      <c r="L80" s="9"/>
-      <c r="M80" s="9"/>
-      <c r="N80" s="9"/>
-      <c r="O80" s="9"/>
+      <c r="A80" s="47">
+        <v>46077.0</v>
+      </c>
+      <c r="B80" s="11"/>
+      <c r="C80" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="11"/>
+      <c r="K80" s="11"/>
+      <c r="L80" s="11"/>
+      <c r="M80" s="11"/>
+      <c r="N80" s="11"/>
+      <c r="O80" s="14"/>
       <c r="P80" s="9"/>
       <c r="Q80" s="4"/>
       <c r="R80" s="9"/>
@@ -3910,21 +3965,11 @@
       <c r="AH80" s="9"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="54"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="9"/>
-      <c r="J81" s="9"/>
-      <c r="K81" s="9"/>
-      <c r="L81" s="9"/>
-      <c r="M81" s="9"/>
-      <c r="N81" s="9"/>
-      <c r="O81" s="9"/>
+      <c r="A81" s="27"/>
+      <c r="C81" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="O81" s="22"/>
       <c r="P81" s="9"/>
       <c r="Q81" s="4"/>
       <c r="R81" s="9"/>
@@ -3946,21 +3991,23 @@
       <c r="AH81" s="9"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="54"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-      <c r="I82" s="9"/>
-      <c r="J82" s="9"/>
-      <c r="K82" s="9"/>
-      <c r="L82" s="9"/>
-      <c r="M82" s="9"/>
-      <c r="N82" s="9"/>
-      <c r="O82" s="9"/>
+      <c r="A82" s="29"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="D82" s="16"/>
+      <c r="E82" s="16"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="16"/>
+      <c r="H82" s="16"/>
+      <c r="I82" s="16"/>
+      <c r="J82" s="16"/>
+      <c r="K82" s="16"/>
+      <c r="L82" s="16"/>
+      <c r="M82" s="16"/>
+      <c r="N82" s="16"/>
+      <c r="O82" s="18"/>
       <c r="P82" s="9"/>
       <c r="Q82" s="4"/>
       <c r="R82" s="9"/>
@@ -3982,21 +4029,23 @@
       <c r="AH82" s="9"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="54"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
+      <c r="A83" s="47"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
       <c r="F83" s="9"/>
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
-      <c r="I83" s="9"/>
-      <c r="J83" s="9"/>
-      <c r="K83" s="9"/>
-      <c r="L83" s="9"/>
-      <c r="M83" s="9"/>
-      <c r="N83" s="9"/>
-      <c r="O83" s="9"/>
+      <c r="I83" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="J83" s="11"/>
+      <c r="K83" s="11"/>
+      <c r="L83" s="11"/>
+      <c r="M83" s="11"/>
+      <c r="N83" s="11"/>
+      <c r="O83" s="14"/>
       <c r="P83" s="9"/>
       <c r="Q83" s="4"/>
       <c r="R83" s="9"/>
@@ -4018,21 +4067,23 @@
       <c r="AH83" s="9"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="54"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="9"/>
-      <c r="J84" s="9"/>
-      <c r="K84" s="9"/>
-      <c r="L84" s="9"/>
-      <c r="M84" s="9"/>
-      <c r="N84" s="9"/>
-      <c r="O84" s="9"/>
+      <c r="A84" s="29"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="16"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="25"/>
+      <c r="H84" s="25"/>
+      <c r="I84" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="J84" s="16"/>
+      <c r="K84" s="16"/>
+      <c r="L84" s="16"/>
+      <c r="M84" s="16"/>
+      <c r="N84" s="16"/>
+      <c r="O84" s="18"/>
       <c r="P84" s="9"/>
       <c r="Q84" s="4"/>
       <c r="R84" s="9"/>
@@ -4054,21 +4105,27 @@
       <c r="AH84" s="9"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="54"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="9"/>
-      <c r="I85" s="9"/>
-      <c r="J85" s="9"/>
-      <c r="K85" s="9"/>
-      <c r="L85" s="9"/>
-      <c r="M85" s="9"/>
-      <c r="N85" s="9"/>
-      <c r="O85" s="9"/>
+      <c r="A85" s="47">
+        <v>46084.0</v>
+      </c>
+      <c r="B85" s="11"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="E85" s="11"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="11"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="11"/>
+      <c r="K85" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="L85" s="11"/>
+      <c r="M85" s="11"/>
+      <c r="N85" s="11"/>
+      <c r="O85" s="14"/>
       <c r="P85" s="9"/>
       <c r="Q85" s="4"/>
       <c r="R85" s="9"/>
@@ -4090,21 +4147,11 @@
       <c r="AH85" s="9"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="54"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="9"/>
-      <c r="H86" s="9"/>
-      <c r="I86" s="9"/>
-      <c r="J86" s="9"/>
-      <c r="K86" s="9"/>
-      <c r="L86" s="9"/>
-      <c r="M86" s="9"/>
-      <c r="N86" s="9"/>
-      <c r="O86" s="9"/>
+      <c r="A86" s="27"/>
+      <c r="D86" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="O86" s="22"/>
       <c r="P86" s="9"/>
       <c r="Q86" s="4"/>
       <c r="R86" s="9"/>
@@ -4126,21 +4173,11 @@
       <c r="AH86" s="9"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="54"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="9"/>
-      <c r="F87" s="9"/>
-      <c r="G87" s="9"/>
-      <c r="H87" s="9"/>
-      <c r="I87" s="9"/>
-      <c r="J87" s="9"/>
-      <c r="K87" s="9"/>
-      <c r="L87" s="9"/>
-      <c r="M87" s="9"/>
-      <c r="N87" s="9"/>
-      <c r="O87" s="9"/>
+      <c r="A87" s="27"/>
+      <c r="D87" s="55" t="s">
+        <v>130</v>
+      </c>
+      <c r="O87" s="22"/>
       <c r="P87" s="9"/>
       <c r="Q87" s="4"/>
       <c r="R87" s="9"/>
@@ -4162,21 +4199,14 @@
       <c r="AH87" s="9"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="54"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="9"/>
-      <c r="J88" s="9"/>
-      <c r="K88" s="9"/>
-      <c r="L88" s="9"/>
-      <c r="M88" s="9"/>
-      <c r="N88" s="9"/>
-      <c r="O88" s="9"/>
+      <c r="A88" s="27"/>
+      <c r="D88" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="K88" s="56" t="s">
+        <v>132</v>
+      </c>
+      <c r="O88" s="22"/>
       <c r="P88" s="9"/>
       <c r="Q88" s="4"/>
       <c r="R88" s="9"/>
@@ -4198,21 +4228,23 @@
       <c r="AH88" s="9"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="54"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="9"/>
-      <c r="D89" s="9"/>
-      <c r="E89" s="9"/>
-      <c r="F89" s="9"/>
-      <c r="G89" s="9"/>
-      <c r="H89" s="9"/>
-      <c r="I89" s="9"/>
-      <c r="J89" s="9"/>
-      <c r="K89" s="9"/>
-      <c r="L89" s="9"/>
-      <c r="M89" s="9"/>
-      <c r="N89" s="9"/>
-      <c r="O89" s="9"/>
+      <c r="A89" s="29"/>
+      <c r="B89" s="16"/>
+      <c r="C89" s="16"/>
+      <c r="D89" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="E89" s="16"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="16"/>
+      <c r="H89" s="16"/>
+      <c r="I89" s="16"/>
+      <c r="J89" s="16"/>
+      <c r="K89" s="16"/>
+      <c r="L89" s="16"/>
+      <c r="M89" s="16"/>
+      <c r="N89" s="16"/>
+      <c r="O89" s="18"/>
       <c r="P89" s="9"/>
       <c r="Q89" s="4"/>
       <c r="R89" s="9"/>
@@ -4234,7 +4266,7 @@
       <c r="AH89" s="9"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="54"/>
+      <c r="A90" s="58"/>
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
@@ -4270,7 +4302,7 @@
       <c r="AH90" s="9"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="54"/>
+      <c r="A91" s="58"/>
       <c r="B91" s="9"/>
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
@@ -4306,7 +4338,7 @@
       <c r="AH91" s="9"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="54"/>
+      <c r="A92" s="58"/>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
@@ -4342,7 +4374,7 @@
       <c r="AH92" s="9"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="54"/>
+      <c r="A93" s="58"/>
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
@@ -4378,7 +4410,7 @@
       <c r="AH93" s="9"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="54"/>
+      <c r="A94" s="58"/>
       <c r="B94" s="9"/>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
@@ -4414,7 +4446,7 @@
       <c r="AH94" s="9"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="54"/>
+      <c r="A95" s="58"/>
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
@@ -4450,7 +4482,7 @@
       <c r="AH95" s="9"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="54"/>
+      <c r="A96" s="58"/>
       <c r="B96" s="9"/>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
@@ -4486,7 +4518,7 @@
       <c r="AH96" s="9"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="54"/>
+      <c r="A97" s="58"/>
       <c r="B97" s="9"/>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
@@ -4522,7 +4554,7 @@
       <c r="AH97" s="9"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="54"/>
+      <c r="A98" s="58"/>
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
@@ -4558,7 +4590,7 @@
       <c r="AH98" s="9"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="54"/>
+      <c r="A99" s="58"/>
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
@@ -4594,7 +4626,7 @@
       <c r="AH99" s="9"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="54"/>
+      <c r="A100" s="58"/>
       <c r="B100" s="9"/>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
@@ -4630,7 +4662,7 @@
       <c r="AH100" s="9"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="54"/>
+      <c r="A101" s="58"/>
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
@@ -4666,7 +4698,7 @@
       <c r="AH101" s="9"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="54"/>
+      <c r="A102" s="58"/>
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
@@ -4702,7 +4734,7 @@
       <c r="AH102" s="9"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="54"/>
+      <c r="A103" s="58"/>
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
@@ -4738,7 +4770,7 @@
       <c r="AH103" s="9"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="54"/>
+      <c r="A104" s="58"/>
       <c r="B104" s="9"/>
       <c r="C104" s="9"/>
       <c r="D104" s="9"/>
@@ -4774,7 +4806,7 @@
       <c r="AH104" s="9"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="54"/>
+      <c r="A105" s="58"/>
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
       <c r="D105" s="9"/>
@@ -4810,7 +4842,7 @@
       <c r="AH105" s="9"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="54"/>
+      <c r="A106" s="58"/>
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
@@ -4846,7 +4878,7 @@
       <c r="AH106" s="9"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="54"/>
+      <c r="A107" s="58"/>
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
@@ -4882,7 +4914,7 @@
       <c r="AH107" s="9"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="54"/>
+      <c r="A108" s="58"/>
       <c r="B108" s="9"/>
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
@@ -4918,7 +4950,7 @@
       <c r="AH108" s="9"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="54"/>
+      <c r="A109" s="58"/>
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
@@ -4954,7 +4986,7 @@
       <c r="AH109" s="9"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="54"/>
+      <c r="A110" s="58"/>
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
@@ -4990,7 +5022,7 @@
       <c r="AH110" s="9"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="54"/>
+      <c r="A111" s="58"/>
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
@@ -5026,7 +5058,7 @@
       <c r="AH111" s="9"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="54"/>
+      <c r="A112" s="58"/>
       <c r="B112" s="9"/>
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
@@ -5062,7 +5094,7 @@
       <c r="AH112" s="9"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="54"/>
+      <c r="A113" s="58"/>
       <c r="B113" s="9"/>
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
@@ -5098,7 +5130,7 @@
       <c r="AH113" s="9"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="54"/>
+      <c r="A114" s="58"/>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
@@ -5134,7 +5166,7 @@
       <c r="AH114" s="9"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="54"/>
+      <c r="A115" s="58"/>
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
@@ -5170,7 +5202,7 @@
       <c r="AH115" s="9"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="54"/>
+      <c r="A116" s="58"/>
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
@@ -5206,7 +5238,7 @@
       <c r="AH116" s="9"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="54"/>
+      <c r="A117" s="58"/>
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
@@ -5242,7 +5274,7 @@
       <c r="AH117" s="9"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="54"/>
+      <c r="A118" s="58"/>
       <c r="B118" s="9"/>
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
@@ -5278,7 +5310,7 @@
       <c r="AH118" s="9"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="54"/>
+      <c r="A119" s="58"/>
       <c r="B119" s="9"/>
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
@@ -5314,7 +5346,7 @@
       <c r="AH119" s="9"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="54"/>
+      <c r="A120" s="58"/>
       <c r="B120" s="9"/>
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
@@ -5350,7 +5382,7 @@
       <c r="AH120" s="9"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="54"/>
+      <c r="A121" s="58"/>
       <c r="B121" s="9"/>
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
@@ -5386,7 +5418,7 @@
       <c r="AH121" s="9"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="54"/>
+      <c r="A122" s="58"/>
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
@@ -5422,7 +5454,7 @@
       <c r="AH122" s="9"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="54"/>
+      <c r="A123" s="58"/>
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
@@ -5458,7 +5490,7 @@
       <c r="AH123" s="9"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="54"/>
+      <c r="A124" s="58"/>
       <c r="B124" s="9"/>
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
@@ -5494,7 +5526,7 @@
       <c r="AH124" s="9"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="54"/>
+      <c r="A125" s="58"/>
       <c r="B125" s="9"/>
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
@@ -5530,7 +5562,7 @@
       <c r="AH125" s="9"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="54"/>
+      <c r="A126" s="58"/>
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
@@ -5566,7 +5598,7 @@
       <c r="AH126" s="9"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="54"/>
+      <c r="A127" s="58"/>
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
@@ -5602,7 +5634,7 @@
       <c r="AH127" s="9"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="54"/>
+      <c r="A128" s="58"/>
       <c r="B128" s="9"/>
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
@@ -5638,7 +5670,7 @@
       <c r="AH128" s="9"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="54"/>
+      <c r="A129" s="58"/>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
       <c r="D129" s="9"/>
@@ -5674,7 +5706,7 @@
       <c r="AH129" s="9"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="54"/>
+      <c r="A130" s="58"/>
       <c r="B130" s="9"/>
       <c r="C130" s="9"/>
       <c r="D130" s="9"/>
@@ -5710,7 +5742,7 @@
       <c r="AH130" s="9"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="54"/>
+      <c r="A131" s="58"/>
       <c r="B131" s="9"/>
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
@@ -5746,7 +5778,7 @@
       <c r="AH131" s="9"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="54"/>
+      <c r="A132" s="58"/>
       <c r="B132" s="9"/>
       <c r="C132" s="9"/>
       <c r="D132" s="9"/>
@@ -5782,7 +5814,7 @@
       <c r="AH132" s="9"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="54"/>
+      <c r="A133" s="58"/>
       <c r="B133" s="9"/>
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
@@ -5818,7 +5850,7 @@
       <c r="AH133" s="9"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="54"/>
+      <c r="A134" s="58"/>
       <c r="B134" s="9"/>
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
@@ -5854,7 +5886,7 @@
       <c r="AH134" s="9"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="54"/>
+      <c r="A135" s="58"/>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
@@ -5890,7 +5922,7 @@
       <c r="AH135" s="9"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="54"/>
+      <c r="A136" s="58"/>
       <c r="B136" s="9"/>
       <c r="C136" s="9"/>
       <c r="D136" s="9"/>
@@ -5926,7 +5958,7 @@
       <c r="AH136" s="9"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="54"/>
+      <c r="A137" s="58"/>
       <c r="B137" s="9"/>
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
@@ -5962,7 +5994,7 @@
       <c r="AH137" s="9"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="54"/>
+      <c r="A138" s="58"/>
       <c r="B138" s="9"/>
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
@@ -5998,7 +6030,7 @@
       <c r="AH138" s="9"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="54"/>
+      <c r="A139" s="58"/>
       <c r="B139" s="9"/>
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
@@ -6034,7 +6066,7 @@
       <c r="AH139" s="9"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="54"/>
+      <c r="A140" s="58"/>
       <c r="B140" s="9"/>
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
@@ -6070,7 +6102,7 @@
       <c r="AH140" s="9"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="54"/>
+      <c r="A141" s="58"/>
       <c r="B141" s="9"/>
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
@@ -6106,7 +6138,7 @@
       <c r="AH141" s="9"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="54"/>
+      <c r="A142" s="58"/>
       <c r="B142" s="9"/>
       <c r="C142" s="9"/>
       <c r="D142" s="9"/>
@@ -6142,7 +6174,7 @@
       <c r="AH142" s="9"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="54"/>
+      <c r="A143" s="58"/>
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
       <c r="D143" s="9"/>
@@ -6178,7 +6210,7 @@
       <c r="AH143" s="9"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="54"/>
+      <c r="A144" s="58"/>
       <c r="B144" s="9"/>
       <c r="C144" s="9"/>
       <c r="D144" s="9"/>
@@ -6214,7 +6246,7 @@
       <c r="AH144" s="9"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="54"/>
+      <c r="A145" s="58"/>
       <c r="B145" s="9"/>
       <c r="C145" s="9"/>
       <c r="D145" s="9"/>
@@ -6250,7 +6282,7 @@
       <c r="AH145" s="9"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="54"/>
+      <c r="A146" s="58"/>
       <c r="B146" s="9"/>
       <c r="C146" s="9"/>
       <c r="D146" s="9"/>
@@ -6286,7 +6318,7 @@
       <c r="AH146" s="9"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="54"/>
+      <c r="A147" s="58"/>
       <c r="B147" s="9"/>
       <c r="C147" s="9"/>
       <c r="D147" s="9"/>
@@ -6322,7 +6354,7 @@
       <c r="AH147" s="9"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="54"/>
+      <c r="A148" s="58"/>
       <c r="B148" s="9"/>
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
@@ -6358,7 +6390,7 @@
       <c r="AH148" s="9"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="54"/>
+      <c r="A149" s="58"/>
       <c r="B149" s="9"/>
       <c r="C149" s="9"/>
       <c r="D149" s="9"/>
@@ -6394,7 +6426,7 @@
       <c r="AH149" s="9"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="54"/>
+      <c r="A150" s="58"/>
       <c r="B150" s="9"/>
       <c r="C150" s="9"/>
       <c r="D150" s="9"/>
@@ -6430,7 +6462,7 @@
       <c r="AH150" s="9"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="54"/>
+      <c r="A151" s="58"/>
       <c r="B151" s="9"/>
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
@@ -6466,7 +6498,7 @@
       <c r="AH151" s="9"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="54"/>
+      <c r="A152" s="58"/>
       <c r="B152" s="9"/>
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
@@ -6502,7 +6534,7 @@
       <c r="AH152" s="9"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="54"/>
+      <c r="A153" s="58"/>
       <c r="B153" s="9"/>
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
@@ -6538,7 +6570,7 @@
       <c r="AH153" s="9"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="54"/>
+      <c r="A154" s="58"/>
       <c r="B154" s="9"/>
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
@@ -6574,7 +6606,7 @@
       <c r="AH154" s="9"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="54"/>
+      <c r="A155" s="58"/>
       <c r="B155" s="9"/>
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
@@ -6610,7 +6642,7 @@
       <c r="AH155" s="9"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="54"/>
+      <c r="A156" s="58"/>
       <c r="B156" s="9"/>
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
@@ -6646,7 +6678,7 @@
       <c r="AH156" s="9"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="54"/>
+      <c r="A157" s="58"/>
       <c r="B157" s="9"/>
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
@@ -6682,7 +6714,7 @@
       <c r="AH157" s="9"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="54"/>
+      <c r="A158" s="58"/>
       <c r="B158" s="9"/>
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
@@ -6718,7 +6750,7 @@
       <c r="AH158" s="9"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="54"/>
+      <c r="A159" s="58"/>
       <c r="B159" s="9"/>
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
@@ -6754,7 +6786,7 @@
       <c r="AH159" s="9"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="54"/>
+      <c r="A160" s="58"/>
       <c r="B160" s="9"/>
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
@@ -6790,7 +6822,7 @@
       <c r="AH160" s="9"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="54"/>
+      <c r="A161" s="58"/>
       <c r="B161" s="9"/>
       <c r="C161" s="9"/>
       <c r="D161" s="9"/>
@@ -6826,7 +6858,7 @@
       <c r="AH161" s="9"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="54"/>
+      <c r="A162" s="58"/>
       <c r="B162" s="9"/>
       <c r="C162" s="9"/>
       <c r="D162" s="9"/>
@@ -6862,7 +6894,7 @@
       <c r="AH162" s="9"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="54"/>
+      <c r="A163" s="58"/>
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
@@ -6898,7 +6930,7 @@
       <c r="AH163" s="9"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="54"/>
+      <c r="A164" s="58"/>
       <c r="B164" s="9"/>
       <c r="C164" s="9"/>
       <c r="D164" s="9"/>
@@ -6934,7 +6966,7 @@
       <c r="AH164" s="9"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="54"/>
+      <c r="A165" s="58"/>
       <c r="B165" s="9"/>
       <c r="C165" s="9"/>
       <c r="D165" s="9"/>
@@ -6970,7 +7002,7 @@
       <c r="AH165" s="9"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="54"/>
+      <c r="A166" s="58"/>
       <c r="B166" s="9"/>
       <c r="C166" s="9"/>
       <c r="D166" s="9"/>
@@ -7006,7 +7038,7 @@
       <c r="AH166" s="9"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="54"/>
+      <c r="A167" s="58"/>
       <c r="B167" s="9"/>
       <c r="C167" s="9"/>
       <c r="D167" s="9"/>
@@ -7042,7 +7074,7 @@
       <c r="AH167" s="9"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="54"/>
+      <c r="A168" s="58"/>
       <c r="B168" s="9"/>
       <c r="C168" s="9"/>
       <c r="D168" s="9"/>
@@ -7078,7 +7110,7 @@
       <c r="AH168" s="9"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="54"/>
+      <c r="A169" s="58"/>
       <c r="B169" s="9"/>
       <c r="C169" s="9"/>
       <c r="D169" s="9"/>
@@ -7114,7 +7146,7 @@
       <c r="AH169" s="9"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="54"/>
+      <c r="A170" s="58"/>
       <c r="B170" s="9"/>
       <c r="C170" s="9"/>
       <c r="D170" s="9"/>
@@ -7150,7 +7182,7 @@
       <c r="AH170" s="9"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="54"/>
+      <c r="A171" s="58"/>
       <c r="B171" s="9"/>
       <c r="C171" s="9"/>
       <c r="D171" s="9"/>
@@ -7186,7 +7218,7 @@
       <c r="AH171" s="9"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="54"/>
+      <c r="A172" s="58"/>
       <c r="B172" s="9"/>
       <c r="C172" s="9"/>
       <c r="D172" s="9"/>
@@ -7222,7 +7254,7 @@
       <c r="AH172" s="9"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="54"/>
+      <c r="A173" s="58"/>
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
       <c r="D173" s="9"/>
@@ -7258,7 +7290,7 @@
       <c r="AH173" s="9"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="54"/>
+      <c r="A174" s="58"/>
       <c r="B174" s="9"/>
       <c r="C174" s="9"/>
       <c r="D174" s="9"/>
@@ -7294,7 +7326,7 @@
       <c r="AH174" s="9"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="54"/>
+      <c r="A175" s="58"/>
       <c r="B175" s="9"/>
       <c r="C175" s="9"/>
       <c r="D175" s="9"/>
@@ -7330,7 +7362,7 @@
       <c r="AH175" s="9"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="54"/>
+      <c r="A176" s="58"/>
       <c r="B176" s="9"/>
       <c r="C176" s="9"/>
       <c r="D176" s="9"/>
@@ -7366,7 +7398,7 @@
       <c r="AH176" s="9"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="54"/>
+      <c r="A177" s="58"/>
       <c r="B177" s="9"/>
       <c r="C177" s="9"/>
       <c r="D177" s="9"/>
@@ -7402,7 +7434,7 @@
       <c r="AH177" s="9"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="54"/>
+      <c r="A178" s="58"/>
       <c r="B178" s="9"/>
       <c r="C178" s="9"/>
       <c r="D178" s="9"/>
@@ -7438,7 +7470,7 @@
       <c r="AH178" s="9"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="54"/>
+      <c r="A179" s="58"/>
       <c r="B179" s="9"/>
       <c r="C179" s="9"/>
       <c r="D179" s="9"/>
@@ -7474,7 +7506,7 @@
       <c r="AH179" s="9"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="54"/>
+      <c r="A180" s="58"/>
       <c r="B180" s="9"/>
       <c r="C180" s="9"/>
       <c r="D180" s="9"/>
@@ -7510,7 +7542,7 @@
       <c r="AH180" s="9"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="54"/>
+      <c r="A181" s="58"/>
       <c r="B181" s="9"/>
       <c r="C181" s="9"/>
       <c r="D181" s="9"/>
@@ -7546,7 +7578,7 @@
       <c r="AH181" s="9"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="54"/>
+      <c r="A182" s="58"/>
       <c r="B182" s="9"/>
       <c r="C182" s="9"/>
       <c r="D182" s="9"/>
@@ -7582,7 +7614,7 @@
       <c r="AH182" s="9"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="54"/>
+      <c r="A183" s="58"/>
       <c r="B183" s="9"/>
       <c r="C183" s="9"/>
       <c r="D183" s="9"/>
@@ -7618,7 +7650,7 @@
       <c r="AH183" s="9"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="54"/>
+      <c r="A184" s="58"/>
       <c r="B184" s="9"/>
       <c r="C184" s="9"/>
       <c r="D184" s="9"/>
@@ -7654,7 +7686,7 @@
       <c r="AH184" s="9"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="54"/>
+      <c r="A185" s="58"/>
       <c r="B185" s="9"/>
       <c r="C185" s="9"/>
       <c r="D185" s="9"/>
@@ -7690,7 +7722,7 @@
       <c r="AH185" s="9"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="54"/>
+      <c r="A186" s="58"/>
       <c r="B186" s="9"/>
       <c r="C186" s="9"/>
       <c r="D186" s="9"/>
@@ -7726,7 +7758,7 @@
       <c r="AH186" s="9"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="54"/>
+      <c r="A187" s="58"/>
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
       <c r="D187" s="9"/>
@@ -7762,7 +7794,7 @@
       <c r="AH187" s="9"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="54"/>
+      <c r="A188" s="58"/>
       <c r="B188" s="9"/>
       <c r="C188" s="9"/>
       <c r="D188" s="9"/>
@@ -7798,7 +7830,7 @@
       <c r="AH188" s="9"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="54"/>
+      <c r="A189" s="58"/>
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
       <c r="D189" s="9"/>
@@ -7834,7 +7866,7 @@
       <c r="AH189" s="9"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="54"/>
+      <c r="A190" s="58"/>
       <c r="B190" s="9"/>
       <c r="C190" s="9"/>
       <c r="D190" s="9"/>
@@ -7870,7 +7902,7 @@
       <c r="AH190" s="9"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="54"/>
+      <c r="A191" s="58"/>
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
       <c r="D191" s="9"/>
@@ -7906,7 +7938,7 @@
       <c r="AH191" s="9"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="54"/>
+      <c r="A192" s="58"/>
       <c r="B192" s="9"/>
       <c r="C192" s="9"/>
       <c r="D192" s="9"/>
@@ -7942,7 +7974,7 @@
       <c r="AH192" s="9"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="54"/>
+      <c r="A193" s="58"/>
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
       <c r="D193" s="9"/>
@@ -7978,7 +8010,7 @@
       <c r="AH193" s="9"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="54"/>
+      <c r="A194" s="58"/>
       <c r="B194" s="9"/>
       <c r="C194" s="9"/>
       <c r="D194" s="9"/>
@@ -8014,7 +8046,7 @@
       <c r="AH194" s="9"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="54"/>
+      <c r="A195" s="58"/>
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
       <c r="D195" s="9"/>
@@ -8050,7 +8082,7 @@
       <c r="AH195" s="9"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="54"/>
+      <c r="A196" s="58"/>
       <c r="B196" s="9"/>
       <c r="C196" s="9"/>
       <c r="D196" s="9"/>
@@ -8086,7 +8118,7 @@
       <c r="AH196" s="9"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="54"/>
+      <c r="A197" s="58"/>
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
       <c r="D197" s="9"/>
@@ -8122,7 +8154,7 @@
       <c r="AH197" s="9"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="54"/>
+      <c r="A198" s="58"/>
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
       <c r="D198" s="9"/>
@@ -8158,7 +8190,7 @@
       <c r="AH198" s="9"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="54"/>
+      <c r="A199" s="58"/>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
       <c r="D199" s="9"/>
@@ -8194,7 +8226,7 @@
       <c r="AH199" s="9"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="54"/>
+      <c r="A200" s="58"/>
       <c r="B200" s="9"/>
       <c r="C200" s="9"/>
       <c r="D200" s="9"/>
@@ -8230,7 +8262,7 @@
       <c r="AH200" s="9"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="54"/>
+      <c r="A201" s="58"/>
       <c r="B201" s="9"/>
       <c r="C201" s="9"/>
       <c r="D201" s="9"/>
@@ -8266,7 +8298,7 @@
       <c r="AH201" s="9"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="54"/>
+      <c r="A202" s="58"/>
       <c r="B202" s="9"/>
       <c r="C202" s="9"/>
       <c r="D202" s="9"/>
@@ -8302,7 +8334,7 @@
       <c r="AH202" s="9"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="54"/>
+      <c r="A203" s="58"/>
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
       <c r="D203" s="9"/>
@@ -8338,7 +8370,7 @@
       <c r="AH203" s="9"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="54"/>
+      <c r="A204" s="58"/>
       <c r="B204" s="9"/>
       <c r="C204" s="9"/>
       <c r="D204" s="9"/>
@@ -8374,7 +8406,7 @@
       <c r="AH204" s="9"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="54"/>
+      <c r="A205" s="58"/>
       <c r="B205" s="9"/>
       <c r="C205" s="9"/>
       <c r="D205" s="9"/>
@@ -8410,7 +8442,7 @@
       <c r="AH205" s="9"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="54"/>
+      <c r="A206" s="58"/>
       <c r="B206" s="9"/>
       <c r="C206" s="9"/>
       <c r="D206" s="9"/>
@@ -8446,7 +8478,7 @@
       <c r="AH206" s="9"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="54"/>
+      <c r="A207" s="58"/>
       <c r="B207" s="9"/>
       <c r="C207" s="9"/>
       <c r="D207" s="9"/>
@@ -8482,7 +8514,7 @@
       <c r="AH207" s="9"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="54"/>
+      <c r="A208" s="58"/>
       <c r="B208" s="9"/>
       <c r="C208" s="9"/>
       <c r="D208" s="9"/>
@@ -8518,7 +8550,7 @@
       <c r="AH208" s="9"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="54"/>
+      <c r="A209" s="58"/>
       <c r="B209" s="9"/>
       <c r="C209" s="9"/>
       <c r="D209" s="9"/>
@@ -8554,7 +8586,7 @@
       <c r="AH209" s="9"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="54"/>
+      <c r="A210" s="58"/>
       <c r="B210" s="9"/>
       <c r="C210" s="9"/>
       <c r="D210" s="9"/>
@@ -8590,7 +8622,7 @@
       <c r="AH210" s="9"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="54"/>
+      <c r="A211" s="58"/>
       <c r="B211" s="9"/>
       <c r="C211" s="9"/>
       <c r="D211" s="9"/>
@@ -8626,7 +8658,7 @@
       <c r="AH211" s="9"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="54"/>
+      <c r="A212" s="58"/>
       <c r="B212" s="9"/>
       <c r="C212" s="9"/>
       <c r="D212" s="9"/>
@@ -8662,7 +8694,7 @@
       <c r="AH212" s="9"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="54"/>
+      <c r="A213" s="58"/>
       <c r="B213" s="9"/>
       <c r="C213" s="9"/>
       <c r="D213" s="9"/>
@@ -8698,7 +8730,7 @@
       <c r="AH213" s="9"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="54"/>
+      <c r="A214" s="58"/>
       <c r="B214" s="9"/>
       <c r="C214" s="9"/>
       <c r="D214" s="9"/>
@@ -8734,7 +8766,7 @@
       <c r="AH214" s="9"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="54"/>
+      <c r="A215" s="58"/>
       <c r="B215" s="9"/>
       <c r="C215" s="9"/>
       <c r="D215" s="9"/>
@@ -8770,7 +8802,7 @@
       <c r="AH215" s="9"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="54"/>
+      <c r="A216" s="58"/>
       <c r="B216" s="9"/>
       <c r="C216" s="9"/>
       <c r="D216" s="9"/>
@@ -8806,7 +8838,7 @@
       <c r="AH216" s="9"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="54"/>
+      <c r="A217" s="58"/>
       <c r="B217" s="9"/>
       <c r="C217" s="9"/>
       <c r="D217" s="9"/>
@@ -8842,7 +8874,7 @@
       <c r="AH217" s="9"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="54"/>
+      <c r="A218" s="58"/>
       <c r="B218" s="9"/>
       <c r="C218" s="9"/>
       <c r="D218" s="9"/>
@@ -8878,7 +8910,7 @@
       <c r="AH218" s="9"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="54"/>
+      <c r="A219" s="58"/>
       <c r="B219" s="9"/>
       <c r="C219" s="9"/>
       <c r="D219" s="9"/>
@@ -8914,7 +8946,7 @@
       <c r="AH219" s="9"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="54"/>
+      <c r="A220" s="58"/>
       <c r="B220" s="9"/>
       <c r="C220" s="9"/>
       <c r="D220" s="9"/>
@@ -8950,7 +8982,7 @@
       <c r="AH220" s="9"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="54"/>
+      <c r="A221" s="58"/>
       <c r="B221" s="9"/>
       <c r="C221" s="9"/>
       <c r="D221" s="9"/>
@@ -8986,7 +9018,7 @@
       <c r="AH221" s="9"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="54"/>
+      <c r="A222" s="58"/>
       <c r="B222" s="9"/>
       <c r="C222" s="9"/>
       <c r="D222" s="9"/>
@@ -9022,7 +9054,7 @@
       <c r="AH222" s="9"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="54"/>
+      <c r="A223" s="58"/>
       <c r="B223" s="9"/>
       <c r="C223" s="9"/>
       <c r="D223" s="9"/>
@@ -9058,7 +9090,7 @@
       <c r="AH223" s="9"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="54"/>
+      <c r="A224" s="58"/>
       <c r="B224" s="9"/>
       <c r="C224" s="9"/>
       <c r="D224" s="9"/>
@@ -9094,7 +9126,7 @@
       <c r="AH224" s="9"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="54"/>
+      <c r="A225" s="58"/>
       <c r="B225" s="9"/>
       <c r="C225" s="9"/>
       <c r="D225" s="9"/>
@@ -9130,7 +9162,7 @@
       <c r="AH225" s="9"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="54"/>
+      <c r="A226" s="58"/>
       <c r="B226" s="9"/>
       <c r="C226" s="9"/>
       <c r="D226" s="9"/>
@@ -9166,7 +9198,7 @@
       <c r="AH226" s="9"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="54"/>
+      <c r="A227" s="58"/>
       <c r="B227" s="9"/>
       <c r="C227" s="9"/>
       <c r="D227" s="9"/>
@@ -9202,7 +9234,7 @@
       <c r="AH227" s="9"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="54"/>
+      <c r="A228" s="58"/>
       <c r="B228" s="9"/>
       <c r="C228" s="9"/>
       <c r="D228" s="9"/>
@@ -9238,7 +9270,7 @@
       <c r="AH228" s="9"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="54"/>
+      <c r="A229" s="58"/>
       <c r="B229" s="9"/>
       <c r="C229" s="9"/>
       <c r="D229" s="9"/>
@@ -9274,7 +9306,7 @@
       <c r="AH229" s="9"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="54"/>
+      <c r="A230" s="58"/>
       <c r="B230" s="9"/>
       <c r="C230" s="9"/>
       <c r="D230" s="9"/>
@@ -9310,7 +9342,7 @@
       <c r="AH230" s="9"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="54"/>
+      <c r="A231" s="58"/>
       <c r="B231" s="9"/>
       <c r="C231" s="9"/>
       <c r="D231" s="9"/>
@@ -9346,7 +9378,7 @@
       <c r="AH231" s="9"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="54"/>
+      <c r="A232" s="58"/>
       <c r="B232" s="9"/>
       <c r="C232" s="9"/>
       <c r="D232" s="9"/>
@@ -9382,7 +9414,7 @@
       <c r="AH232" s="9"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="54"/>
+      <c r="A233" s="58"/>
       <c r="B233" s="9"/>
       <c r="C233" s="9"/>
       <c r="D233" s="9"/>
@@ -9418,7 +9450,7 @@
       <c r="AH233" s="9"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="54"/>
+      <c r="A234" s="58"/>
       <c r="B234" s="9"/>
       <c r="C234" s="9"/>
       <c r="D234" s="9"/>
@@ -9454,7 +9486,7 @@
       <c r="AH234" s="9"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="54"/>
+      <c r="A235" s="58"/>
       <c r="B235" s="9"/>
       <c r="C235" s="9"/>
       <c r="D235" s="9"/>
@@ -9490,7 +9522,7 @@
       <c r="AH235" s="9"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="54"/>
+      <c r="A236" s="58"/>
       <c r="B236" s="9"/>
       <c r="C236" s="9"/>
       <c r="D236" s="9"/>
@@ -9526,7 +9558,7 @@
       <c r="AH236" s="9"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="54"/>
+      <c r="A237" s="58"/>
       <c r="B237" s="9"/>
       <c r="C237" s="9"/>
       <c r="D237" s="9"/>
@@ -9562,7 +9594,7 @@
       <c r="AH237" s="9"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="54"/>
+      <c r="A238" s="58"/>
       <c r="B238" s="9"/>
       <c r="C238" s="9"/>
       <c r="D238" s="9"/>
@@ -9598,7 +9630,7 @@
       <c r="AH238" s="9"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="54"/>
+      <c r="A239" s="58"/>
       <c r="B239" s="9"/>
       <c r="C239" s="9"/>
       <c r="D239" s="9"/>
@@ -9634,7 +9666,7 @@
       <c r="AH239" s="9"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="54"/>
+      <c r="A240" s="58"/>
       <c r="B240" s="9"/>
       <c r="C240" s="9"/>
       <c r="D240" s="9"/>
@@ -9670,7 +9702,7 @@
       <c r="AH240" s="9"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="54"/>
+      <c r="A241" s="58"/>
       <c r="B241" s="9"/>
       <c r="C241" s="9"/>
       <c r="D241" s="9"/>
@@ -9706,7 +9738,7 @@
       <c r="AH241" s="9"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="54"/>
+      <c r="A242" s="58"/>
       <c r="B242" s="9"/>
       <c r="C242" s="9"/>
       <c r="D242" s="9"/>
@@ -9742,7 +9774,7 @@
       <c r="AH242" s="9"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="54"/>
+      <c r="A243" s="58"/>
       <c r="B243" s="9"/>
       <c r="C243" s="9"/>
       <c r="D243" s="9"/>
@@ -9778,7 +9810,7 @@
       <c r="AH243" s="9"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="54"/>
+      <c r="A244" s="58"/>
       <c r="B244" s="9"/>
       <c r="C244" s="9"/>
       <c r="D244" s="9"/>
@@ -9814,7 +9846,7 @@
       <c r="AH244" s="9"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="54"/>
+      <c r="A245" s="58"/>
       <c r="B245" s="9"/>
       <c r="C245" s="9"/>
       <c r="D245" s="9"/>
@@ -9850,7 +9882,7 @@
       <c r="AH245" s="9"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="54"/>
+      <c r="A246" s="58"/>
       <c r="B246" s="9"/>
       <c r="C246" s="9"/>
       <c r="D246" s="9"/>
@@ -9886,7 +9918,7 @@
       <c r="AH246" s="9"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="54"/>
+      <c r="A247" s="58"/>
       <c r="B247" s="9"/>
       <c r="C247" s="9"/>
       <c r="D247" s="9"/>
@@ -9922,7 +9954,7 @@
       <c r="AH247" s="9"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="54"/>
+      <c r="A248" s="58"/>
       <c r="B248" s="9"/>
       <c r="C248" s="9"/>
       <c r="D248" s="9"/>
@@ -9958,7 +9990,7 @@
       <c r="AH248" s="9"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="54"/>
+      <c r="A249" s="58"/>
       <c r="B249" s="9"/>
       <c r="C249" s="9"/>
       <c r="D249" s="9"/>
@@ -9994,7 +10026,7 @@
       <c r="AH249" s="9"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="54"/>
+      <c r="A250" s="58"/>
       <c r="B250" s="9"/>
       <c r="C250" s="9"/>
       <c r="D250" s="9"/>
@@ -10030,7 +10062,7 @@
       <c r="AH250" s="9"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="54"/>
+      <c r="A251" s="58"/>
       <c r="B251" s="9"/>
       <c r="C251" s="9"/>
       <c r="D251" s="9"/>
@@ -10066,7 +10098,7 @@
       <c r="AH251" s="9"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="54"/>
+      <c r="A252" s="58"/>
       <c r="B252" s="9"/>
       <c r="C252" s="9"/>
       <c r="D252" s="9"/>
@@ -10102,7 +10134,7 @@
       <c r="AH252" s="9"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="54"/>
+      <c r="A253" s="58"/>
       <c r="B253" s="9"/>
       <c r="C253" s="9"/>
       <c r="D253" s="9"/>
@@ -10138,7 +10170,7 @@
       <c r="AH253" s="9"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="54"/>
+      <c r="A254" s="58"/>
       <c r="B254" s="9"/>
       <c r="C254" s="9"/>
       <c r="D254" s="9"/>
@@ -10174,7 +10206,7 @@
       <c r="AH254" s="9"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="54"/>
+      <c r="A255" s="58"/>
       <c r="B255" s="9"/>
       <c r="C255" s="9"/>
       <c r="D255" s="9"/>
@@ -10210,7 +10242,7 @@
       <c r="AH255" s="9"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="54"/>
+      <c r="A256" s="58"/>
       <c r="B256" s="9"/>
       <c r="C256" s="9"/>
       <c r="D256" s="9"/>
@@ -10246,7 +10278,7 @@
       <c r="AH256" s="9"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="54"/>
+      <c r="A257" s="58"/>
       <c r="B257" s="9"/>
       <c r="C257" s="9"/>
       <c r="D257" s="9"/>
@@ -10282,7 +10314,7 @@
       <c r="AH257" s="9"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="54"/>
+      <c r="A258" s="58"/>
       <c r="B258" s="9"/>
       <c r="C258" s="9"/>
       <c r="D258" s="9"/>
@@ -10318,7 +10350,7 @@
       <c r="AH258" s="9"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="54"/>
+      <c r="A259" s="58"/>
       <c r="B259" s="9"/>
       <c r="C259" s="9"/>
       <c r="D259" s="9"/>
@@ -10354,7 +10386,7 @@
       <c r="AH259" s="9"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="54"/>
+      <c r="A260" s="58"/>
       <c r="B260" s="9"/>
       <c r="C260" s="9"/>
       <c r="D260" s="9"/>
@@ -10390,7 +10422,7 @@
       <c r="AH260" s="9"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="54"/>
+      <c r="A261" s="58"/>
       <c r="B261" s="9"/>
       <c r="C261" s="9"/>
       <c r="D261" s="9"/>
@@ -10426,7 +10458,7 @@
       <c r="AH261" s="9"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="54"/>
+      <c r="A262" s="58"/>
       <c r="B262" s="9"/>
       <c r="C262" s="9"/>
       <c r="D262" s="9"/>
@@ -10461,42 +10493,7 @@
       <c r="AG262" s="9"/>
       <c r="AH262" s="9"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="54"/>
-      <c r="B263" s="9"/>
-      <c r="C263" s="9"/>
-      <c r="D263" s="9"/>
-      <c r="E263" s="9"/>
-      <c r="F263" s="9"/>
-      <c r="G263" s="9"/>
-      <c r="H263" s="9"/>
-      <c r="I263" s="9"/>
-      <c r="J263" s="9"/>
-      <c r="K263" s="9"/>
-      <c r="L263" s="9"/>
-      <c r="M263" s="9"/>
-      <c r="N263" s="9"/>
-      <c r="O263" s="9"/>
-      <c r="P263" s="9"/>
-      <c r="Q263" s="4"/>
-      <c r="R263" s="9"/>
-      <c r="S263" s="9"/>
-      <c r="T263" s="9"/>
-      <c r="U263" s="9"/>
-      <c r="V263" s="9"/>
-      <c r="W263" s="9"/>
-      <c r="X263" s="9"/>
-      <c r="Y263" s="9"/>
-      <c r="Z263" s="9"/>
-      <c r="AA263" s="9"/>
-      <c r="AB263" s="9"/>
-      <c r="AC263" s="9"/>
-      <c r="AD263" s="9"/>
-      <c r="AE263" s="9"/>
-      <c r="AF263" s="9"/>
-      <c r="AG263" s="9"/>
-      <c r="AH263" s="9"/>
-    </row>
+    <row r="263" ht="15.75" customHeight="1"/>
     <row r="264" ht="15.75" customHeight="1"/>
     <row r="265" ht="15.75" customHeight="1"/>
     <row r="266" ht="15.75" customHeight="1"/>
@@ -11234,9 +11231,168 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="274">
+  <mergeCells count="314">
+    <mergeCell ref="H13:H17"/>
+    <mergeCell ref="I13:I17"/>
+    <mergeCell ref="J13:J17"/>
+    <mergeCell ref="K13:K17"/>
+    <mergeCell ref="L13:L17"/>
+    <mergeCell ref="M13:M15"/>
+    <mergeCell ref="O13:O17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="D13:D17"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="F13:F17"/>
+    <mergeCell ref="G13:G17"/>
+    <mergeCell ref="L18:L20"/>
+    <mergeCell ref="M18:M20"/>
+    <mergeCell ref="N18:N20"/>
+    <mergeCell ref="O18:O20"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="J18:J20"/>
+    <mergeCell ref="K18:K20"/>
+    <mergeCell ref="M27:M29"/>
+    <mergeCell ref="N27:N29"/>
+    <mergeCell ref="O27:O29"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="J27:J29"/>
+    <mergeCell ref="K27:K29"/>
+    <mergeCell ref="L27:L29"/>
+    <mergeCell ref="H30:H33"/>
+    <mergeCell ref="I30:I33"/>
+    <mergeCell ref="J30:J33"/>
+    <mergeCell ref="L30:L33"/>
+    <mergeCell ref="M30:M33"/>
+    <mergeCell ref="N30:N33"/>
+    <mergeCell ref="O30:O33"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="G30:G33"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="I34:I37"/>
+    <mergeCell ref="K34:K37"/>
+    <mergeCell ref="L34:L37"/>
+    <mergeCell ref="M34:M37"/>
+    <mergeCell ref="N34:N37"/>
+    <mergeCell ref="O34:O37"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="G34:G37"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="L38:L39"/>
+    <mergeCell ref="M38:M39"/>
+    <mergeCell ref="N38:N39"/>
+    <mergeCell ref="O38:O39"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="H40:H42"/>
+    <mergeCell ref="I40:I42"/>
+    <mergeCell ref="J40:J42"/>
+    <mergeCell ref="K40:K42"/>
+    <mergeCell ref="M40:M42"/>
+    <mergeCell ref="N40:N42"/>
+    <mergeCell ref="O40:O42"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="F40:F42"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="I80:I82"/>
+    <mergeCell ref="J80:J82"/>
+    <mergeCell ref="K80:K82"/>
+    <mergeCell ref="L80:L82"/>
+    <mergeCell ref="M80:M82"/>
+    <mergeCell ref="N80:N82"/>
+    <mergeCell ref="O80:O82"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="B80:B82"/>
+    <mergeCell ref="D80:D82"/>
+    <mergeCell ref="E80:E82"/>
+    <mergeCell ref="F80:F82"/>
+    <mergeCell ref="G80:G82"/>
+    <mergeCell ref="H80:H82"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="I71:I73"/>
+    <mergeCell ref="J71:J73"/>
+    <mergeCell ref="L71:L73"/>
+    <mergeCell ref="M71:M73"/>
+    <mergeCell ref="N71:N73"/>
+    <mergeCell ref="O71:O73"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="B71:B73"/>
+    <mergeCell ref="C71:C73"/>
+    <mergeCell ref="D71:D73"/>
+    <mergeCell ref="E71:E73"/>
+    <mergeCell ref="F71:F73"/>
+    <mergeCell ref="G71:G73"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="I74:I76"/>
+    <mergeCell ref="K74:K76"/>
+    <mergeCell ref="L74:L76"/>
+    <mergeCell ref="M74:M76"/>
+    <mergeCell ref="N74:N76"/>
+    <mergeCell ref="O74:O76"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="B74:B76"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="D74:D76"/>
+    <mergeCell ref="E74:E76"/>
+    <mergeCell ref="F74:F76"/>
+    <mergeCell ref="G74:G76"/>
+    <mergeCell ref="L77:L79"/>
+    <mergeCell ref="M77:M79"/>
+    <mergeCell ref="N77:N79"/>
+    <mergeCell ref="O77:O79"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="D77:D79"/>
+    <mergeCell ref="I77:I79"/>
+    <mergeCell ref="J77:J79"/>
+    <mergeCell ref="K77:K79"/>
+    <mergeCell ref="I85:I89"/>
+    <mergeCell ref="J85:J89"/>
+    <mergeCell ref="L85:L89"/>
+    <mergeCell ref="M85:M89"/>
+    <mergeCell ref="N85:N89"/>
+    <mergeCell ref="O85:O89"/>
+    <mergeCell ref="K85:K87"/>
+    <mergeCell ref="K88:K89"/>
+    <mergeCell ref="A85:A89"/>
+    <mergeCell ref="B85:B89"/>
+    <mergeCell ref="C85:C89"/>
+    <mergeCell ref="E85:E89"/>
+    <mergeCell ref="F85:F89"/>
+    <mergeCell ref="G85:G89"/>
+    <mergeCell ref="H85:H89"/>
     <mergeCell ref="H22:H26"/>
     <mergeCell ref="I22:I26"/>
     <mergeCell ref="J22:J26"/>
@@ -11335,45 +11491,6 @@
     <mergeCell ref="M58:M59"/>
     <mergeCell ref="N58:N59"/>
     <mergeCell ref="O58:O59"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="I71:I73"/>
-    <mergeCell ref="J71:J73"/>
-    <mergeCell ref="L71:L73"/>
-    <mergeCell ref="M71:M73"/>
-    <mergeCell ref="N71:N73"/>
-    <mergeCell ref="O71:O73"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="B71:B73"/>
-    <mergeCell ref="C71:C73"/>
-    <mergeCell ref="D71:D73"/>
-    <mergeCell ref="E71:E73"/>
-    <mergeCell ref="F71:F73"/>
-    <mergeCell ref="G71:G73"/>
-    <mergeCell ref="H74:H76"/>
-    <mergeCell ref="I74:I76"/>
-    <mergeCell ref="K74:K76"/>
-    <mergeCell ref="L74:L76"/>
-    <mergeCell ref="M74:M76"/>
-    <mergeCell ref="N74:N76"/>
-    <mergeCell ref="O74:O76"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="B74:B76"/>
-    <mergeCell ref="C74:C76"/>
-    <mergeCell ref="D74:D76"/>
-    <mergeCell ref="E74:E76"/>
-    <mergeCell ref="F74:F76"/>
-    <mergeCell ref="G74:G76"/>
-    <mergeCell ref="L77:L79"/>
-    <mergeCell ref="M77:M79"/>
-    <mergeCell ref="N77:N79"/>
-    <mergeCell ref="O77:O79"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="D77:D79"/>
-    <mergeCell ref="I77:I79"/>
-    <mergeCell ref="J77:J79"/>
-    <mergeCell ref="K77:K79"/>
     <mergeCell ref="A54:A57"/>
     <mergeCell ref="A58:A59"/>
     <mergeCell ref="B58:B59"/>
@@ -11419,98 +11536,17 @@
     <mergeCell ref="J69:J70"/>
     <mergeCell ref="K69:K70"/>
     <mergeCell ref="L69:L70"/>
-    <mergeCell ref="H13:H17"/>
-    <mergeCell ref="I13:I17"/>
-    <mergeCell ref="J13:J17"/>
-    <mergeCell ref="K13:K17"/>
-    <mergeCell ref="L13:L17"/>
-    <mergeCell ref="M13:M15"/>
-    <mergeCell ref="O13:O17"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="D13:D17"/>
-    <mergeCell ref="E13:E17"/>
-    <mergeCell ref="F13:F17"/>
-    <mergeCell ref="G13:G17"/>
-    <mergeCell ref="L18:L20"/>
-    <mergeCell ref="M18:M20"/>
-    <mergeCell ref="N18:N20"/>
-    <mergeCell ref="O18:O20"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="J18:J20"/>
-    <mergeCell ref="K18:K20"/>
-    <mergeCell ref="M27:M29"/>
-    <mergeCell ref="N27:N29"/>
-    <mergeCell ref="O27:O29"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="J27:J29"/>
-    <mergeCell ref="K27:K29"/>
-    <mergeCell ref="L27:L29"/>
-    <mergeCell ref="H30:H33"/>
-    <mergeCell ref="I30:I33"/>
-    <mergeCell ref="J30:J33"/>
-    <mergeCell ref="L30:L33"/>
-    <mergeCell ref="M30:M33"/>
-    <mergeCell ref="N30:N33"/>
-    <mergeCell ref="O30:O33"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="E30:E33"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="G30:G33"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="I34:I37"/>
-    <mergeCell ref="K34:K37"/>
-    <mergeCell ref="L34:L37"/>
-    <mergeCell ref="M34:M37"/>
-    <mergeCell ref="N34:N37"/>
-    <mergeCell ref="O34:O37"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="F34:F37"/>
-    <mergeCell ref="G34:G37"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="K38:K39"/>
-    <mergeCell ref="L38:L39"/>
-    <mergeCell ref="M38:M39"/>
-    <mergeCell ref="N38:N39"/>
-    <mergeCell ref="O38:O39"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="H40:H42"/>
-    <mergeCell ref="I40:I42"/>
-    <mergeCell ref="J40:J42"/>
-    <mergeCell ref="K40:K42"/>
-    <mergeCell ref="M40:M42"/>
-    <mergeCell ref="N40:N42"/>
-    <mergeCell ref="O40:O42"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="F40:F42"/>
-    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="L83:L84"/>
+    <mergeCell ref="M83:M84"/>
+    <mergeCell ref="N83:N84"/>
+    <mergeCell ref="O83:O84"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="J83:J84"/>
+    <mergeCell ref="K83:K84"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="M61"/>
@@ -11534,58 +11570,58 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="55" t="s">
-        <v>122</v>
-      </c>
-      <c r="B2" s="55" t="s">
-        <v>123</v>
-      </c>
-      <c r="C2" s="55" t="s">
-        <v>124</v>
+      <c r="A2" s="59" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="55" t="s">
-        <v>125</v>
-      </c>
-      <c r="B3" s="55" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" s="55" t="s">
-        <v>127</v>
+      <c r="A3" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="55" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" s="55" t="s">
+      <c r="A4" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="55" t="s">
-        <v>129</v>
+      <c r="C4" s="59" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="55" t="s">
-        <v>130</v>
-      </c>
-      <c r="B5" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>132</v>
+      <c r="A5" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="55" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>135</v>
+      <c r="A6" s="59" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>

--- a/Grade2-Homeworks.xlsx
+++ b/Grade2-Homeworks.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="158">
   <si>
     <t>Date</t>
   </si>
@@ -557,6 +557,40 @@
   </si>
   <si>
     <t>HW Read Ch.3 - AI Summary (Mahavira)</t>
+  </si>
+  <si>
+    <t>Complete AI exercises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepare your own CV &amp; resume in 'markdown' </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fix Copy tracing book (latex) - show it to your parents; Add missing letters; Complete copy tracing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct these songs, breakdown etc. and practice singing together  :
+3 songs (1) Mata nirmala Maheswari (2) Jaag uthe (3) Sharanu gori </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HW: పాత HWs పూర్తి చేయాలి </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ఈ పాటలు, అభ్యాసాలు సరిజేసి సమాధానాలు వ్రాయాలి.
+   - తెలుగు సహజయోగ భజనలు/ పాటలు: (1) శరణుగోరి నీ చరణము (2) మాతా నిర్మల మహేశ్వరి - AI తో ఈ పాటల మీద అభ్యాసాలు/ప్రశ్నలు తయారు చేసాం </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - మూషిక మార్గాలాల కథ; AI తో ప్రతి పదార్థాలు వ్రాసాం; AI తో English అనువాదం, సారాంశాలు    
+   - HW: ఇవి చదివి సరి చేయాలి</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - తెలుగు చందమామ కథలు 
+     - HW: వీలైనపుడు చదవాలి</t>
+  </si>
+  <si>
+    <t>HW: Solve AI exercises (Solving two simple equations)</t>
+  </si>
+  <si>
+    <t>Run the python example with different number of cores from 1 to 4 and note how the time changes (Inverse proportion - Sequential &amp; parallel work )</t>
   </si>
   <si>
     <t>Monday</t>
@@ -801,7 +835,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -946,13 +980,16 @@
     <xf borderId="5" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -4110,7 +4147,7 @@
       </c>
       <c r="B85" s="11"/>
       <c r="C85" s="11"/>
-      <c r="D85" s="54" t="s">
+      <c r="D85" s="48" t="s">
         <v>127</v>
       </c>
       <c r="E85" s="11"/>
@@ -4148,7 +4185,7 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="27"/>
-      <c r="D86" s="55" t="s">
+      <c r="D86" s="49" t="s">
         <v>129</v>
       </c>
       <c r="O86" s="22"/>
@@ -4174,7 +4211,7 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="27"/>
-      <c r="D87" s="55" t="s">
+      <c r="D87" s="49" t="s">
         <v>130</v>
       </c>
       <c r="O87" s="22"/>
@@ -4200,10 +4237,10 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="27"/>
-      <c r="D88" s="55" t="s">
+      <c r="D88" s="54" t="s">
         <v>131</v>
       </c>
-      <c r="K88" s="56" t="s">
+      <c r="K88" s="55" t="s">
         <v>132</v>
       </c>
       <c r="O88" s="22"/>
@@ -4231,7 +4268,7 @@
       <c r="A89" s="29"/>
       <c r="B89" s="16"/>
       <c r="C89" s="16"/>
-      <c r="D89" s="57" t="s">
+      <c r="D89" s="51" t="s">
         <v>133</v>
       </c>
       <c r="E89" s="16"/>
@@ -4266,21 +4303,27 @@
       <c r="AH89" s="9"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="58"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
-      <c r="I90" s="9"/>
-      <c r="J90" s="9"/>
-      <c r="K90" s="9"/>
-      <c r="L90" s="9"/>
-      <c r="M90" s="9"/>
-      <c r="N90" s="9"/>
-      <c r="O90" s="9"/>
+      <c r="A90" s="45">
+        <v>46086.0</v>
+      </c>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="6"/>
+      <c r="M90" s="56" t="s">
+        <v>134</v>
+      </c>
+      <c r="N90" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="O90" s="8"/>
       <c r="P90" s="9"/>
       <c r="Q90" s="4"/>
       <c r="R90" s="9"/>
@@ -4302,21 +4345,27 @@
       <c r="AH90" s="9"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="58"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9"/>
-      <c r="F91" s="9"/>
-      <c r="G91" s="9"/>
-      <c r="H91" s="9"/>
-      <c r="I91" s="9"/>
-      <c r="J91" s="9"/>
-      <c r="K91" s="9"/>
-      <c r="L91" s="9"/>
-      <c r="M91" s="9"/>
-      <c r="N91" s="9"/>
-      <c r="O91" s="9"/>
+      <c r="A91" s="45">
+        <v>46087.0</v>
+      </c>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="F91" s="6"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6"/>
+      <c r="J91" s="6"/>
+      <c r="K91" s="6"/>
+      <c r="L91" s="56" t="s">
+        <v>137</v>
+      </c>
+      <c r="M91" s="6"/>
+      <c r="N91" s="6"/>
+      <c r="O91" s="8"/>
       <c r="P91" s="9"/>
       <c r="Q91" s="4"/>
       <c r="R91" s="9"/>
@@ -4338,21 +4387,25 @@
       <c r="AH91" s="9"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="58"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
-      <c r="I92" s="9"/>
-      <c r="J92" s="9"/>
-      <c r="K92" s="9"/>
-      <c r="L92" s="9"/>
-      <c r="M92" s="9"/>
-      <c r="N92" s="9"/>
-      <c r="O92" s="9"/>
+      <c r="A92" s="47">
+        <v>46091.0</v>
+      </c>
+      <c r="B92" s="11"/>
+      <c r="C92" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11"/>
+      <c r="F92" s="11"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="11"/>
+      <c r="I92" s="11"/>
+      <c r="J92" s="11"/>
+      <c r="K92" s="11"/>
+      <c r="L92" s="11"/>
+      <c r="M92" s="11"/>
+      <c r="N92" s="11"/>
+      <c r="O92" s="14"/>
       <c r="P92" s="9"/>
       <c r="Q92" s="4"/>
       <c r="R92" s="9"/>
@@ -4374,21 +4427,11 @@
       <c r="AH92" s="9"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="58"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="9"/>
-      <c r="D93" s="9"/>
-      <c r="E93" s="9"/>
-      <c r="F93" s="9"/>
-      <c r="G93" s="9"/>
-      <c r="H93" s="9"/>
-      <c r="I93" s="9"/>
-      <c r="J93" s="9"/>
-      <c r="K93" s="9"/>
-      <c r="L93" s="9"/>
-      <c r="M93" s="9"/>
-      <c r="N93" s="9"/>
-      <c r="O93" s="9"/>
+      <c r="A93" s="27"/>
+      <c r="C93" s="54" t="s">
+        <v>139</v>
+      </c>
+      <c r="O93" s="22"/>
       <c r="P93" s="9"/>
       <c r="Q93" s="4"/>
       <c r="R93" s="9"/>
@@ -4410,21 +4453,11 @@
       <c r="AH93" s="9"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="58"/>
-      <c r="B94" s="9"/>
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="9"/>
-      <c r="G94" s="9"/>
-      <c r="H94" s="9"/>
-      <c r="I94" s="9"/>
-      <c r="J94" s="9"/>
-      <c r="K94" s="9"/>
-      <c r="L94" s="9"/>
-      <c r="M94" s="9"/>
-      <c r="N94" s="9"/>
-      <c r="O94" s="9"/>
+      <c r="A94" s="27"/>
+      <c r="C94" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="O94" s="22"/>
       <c r="P94" s="9"/>
       <c r="Q94" s="4"/>
       <c r="R94" s="9"/>
@@ -4446,21 +4479,23 @@
       <c r="AH94" s="9"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="58"/>
-      <c r="B95" s="9"/>
-      <c r="C95" s="9"/>
-      <c r="D95" s="9"/>
-      <c r="E95" s="9"/>
-      <c r="F95" s="9"/>
-      <c r="G95" s="9"/>
-      <c r="H95" s="9"/>
-      <c r="I95" s="9"/>
-      <c r="J95" s="9"/>
-      <c r="K95" s="9"/>
-      <c r="L95" s="9"/>
-      <c r="M95" s="9"/>
-      <c r="N95" s="9"/>
-      <c r="O95" s="9"/>
+      <c r="A95" s="29"/>
+      <c r="B95" s="16"/>
+      <c r="C95" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="D95" s="16"/>
+      <c r="E95" s="16"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="16"/>
+      <c r="H95" s="16"/>
+      <c r="I95" s="16"/>
+      <c r="J95" s="16"/>
+      <c r="K95" s="16"/>
+      <c r="L95" s="16"/>
+      <c r="M95" s="16"/>
+      <c r="N95" s="16"/>
+      <c r="O95" s="18"/>
       <c r="P95" s="9"/>
       <c r="Q95" s="4"/>
       <c r="R95" s="9"/>
@@ -4482,21 +4517,25 @@
       <c r="AH95" s="9"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="58"/>
-      <c r="B96" s="9"/>
-      <c r="C96" s="9"/>
-      <c r="D96" s="9"/>
-      <c r="E96" s="9"/>
-      <c r="F96" s="9"/>
-      <c r="G96" s="9"/>
-      <c r="H96" s="9"/>
-      <c r="I96" s="9"/>
-      <c r="J96" s="9"/>
-      <c r="K96" s="9"/>
-      <c r="L96" s="9"/>
-      <c r="M96" s="9"/>
-      <c r="N96" s="9"/>
-      <c r="O96" s="9"/>
+      <c r="A96" s="47">
+        <v>46098.0</v>
+      </c>
+      <c r="B96" s="11"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="11"/>
+      <c r="G96" s="11"/>
+      <c r="H96" s="11"/>
+      <c r="I96" s="57" t="s">
+        <v>142</v>
+      </c>
+      <c r="J96" s="11"/>
+      <c r="K96" s="11"/>
+      <c r="L96" s="11"/>
+      <c r="M96" s="11"/>
+      <c r="N96" s="11"/>
+      <c r="O96" s="14"/>
       <c r="P96" s="9"/>
       <c r="Q96" s="4"/>
       <c r="R96" s="9"/>
@@ -4518,21 +4557,23 @@
       <c r="AH96" s="9"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="58"/>
-      <c r="B97" s="9"/>
-      <c r="C97" s="9"/>
-      <c r="D97" s="9"/>
-      <c r="E97" s="9"/>
-      <c r="F97" s="9"/>
-      <c r="G97" s="9"/>
-      <c r="H97" s="9"/>
-      <c r="I97" s="9"/>
-      <c r="J97" s="9"/>
-      <c r="K97" s="9"/>
-      <c r="L97" s="9"/>
-      <c r="M97" s="9"/>
-      <c r="N97" s="9"/>
-      <c r="O97" s="9"/>
+      <c r="A97" s="29"/>
+      <c r="B97" s="16"/>
+      <c r="C97" s="16"/>
+      <c r="D97" s="16"/>
+      <c r="E97" s="16"/>
+      <c r="F97" s="25"/>
+      <c r="G97" s="25"/>
+      <c r="H97" s="25"/>
+      <c r="I97" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="J97" s="16"/>
+      <c r="K97" s="16"/>
+      <c r="L97" s="16"/>
+      <c r="M97" s="16"/>
+      <c r="N97" s="16"/>
+      <c r="O97" s="18"/>
       <c r="P97" s="9"/>
       <c r="Q97" s="4"/>
       <c r="R97" s="9"/>
@@ -4554,7 +4595,7 @@
       <c r="AH97" s="9"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="58"/>
+      <c r="A98" s="59"/>
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
@@ -4590,7 +4631,7 @@
       <c r="AH98" s="9"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="58"/>
+      <c r="A99" s="59"/>
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
@@ -4626,7 +4667,7 @@
       <c r="AH99" s="9"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="58"/>
+      <c r="A100" s="59"/>
       <c r="B100" s="9"/>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
@@ -4662,7 +4703,7 @@
       <c r="AH100" s="9"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="58"/>
+      <c r="A101" s="59"/>
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
@@ -4698,7 +4739,7 @@
       <c r="AH101" s="9"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="58"/>
+      <c r="A102" s="59"/>
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
@@ -4734,7 +4775,7 @@
       <c r="AH102" s="9"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="58"/>
+      <c r="A103" s="59"/>
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
@@ -4770,7 +4811,7 @@
       <c r="AH103" s="9"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="58"/>
+      <c r="A104" s="59"/>
       <c r="B104" s="9"/>
       <c r="C104" s="9"/>
       <c r="D104" s="9"/>
@@ -4806,7 +4847,7 @@
       <c r="AH104" s="9"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="58"/>
+      <c r="A105" s="59"/>
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
       <c r="D105" s="9"/>
@@ -4842,7 +4883,7 @@
       <c r="AH105" s="9"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="58"/>
+      <c r="A106" s="59"/>
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
@@ -4878,7 +4919,7 @@
       <c r="AH106" s="9"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="58"/>
+      <c r="A107" s="59"/>
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
@@ -4914,7 +4955,7 @@
       <c r="AH107" s="9"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="58"/>
+      <c r="A108" s="59"/>
       <c r="B108" s="9"/>
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
@@ -4950,7 +4991,7 @@
       <c r="AH108" s="9"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="58"/>
+      <c r="A109" s="59"/>
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
@@ -4986,7 +5027,7 @@
       <c r="AH109" s="9"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="58"/>
+      <c r="A110" s="59"/>
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
@@ -5022,7 +5063,7 @@
       <c r="AH110" s="9"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="58"/>
+      <c r="A111" s="59"/>
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
@@ -5058,7 +5099,7 @@
       <c r="AH111" s="9"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="58"/>
+      <c r="A112" s="59"/>
       <c r="B112" s="9"/>
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
@@ -5094,7 +5135,7 @@
       <c r="AH112" s="9"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="58"/>
+      <c r="A113" s="59"/>
       <c r="B113" s="9"/>
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
@@ -5130,7 +5171,7 @@
       <c r="AH113" s="9"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="58"/>
+      <c r="A114" s="59"/>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
@@ -5166,7 +5207,7 @@
       <c r="AH114" s="9"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="58"/>
+      <c r="A115" s="59"/>
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
@@ -5202,7 +5243,7 @@
       <c r="AH115" s="9"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="58"/>
+      <c r="A116" s="59"/>
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
@@ -5238,7 +5279,7 @@
       <c r="AH116" s="9"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="58"/>
+      <c r="A117" s="59"/>
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
@@ -5274,7 +5315,7 @@
       <c r="AH117" s="9"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="58"/>
+      <c r="A118" s="59"/>
       <c r="B118" s="9"/>
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
@@ -5310,7 +5351,7 @@
       <c r="AH118" s="9"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="58"/>
+      <c r="A119" s="59"/>
       <c r="B119" s="9"/>
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
@@ -5346,7 +5387,7 @@
       <c r="AH119" s="9"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="58"/>
+      <c r="A120" s="59"/>
       <c r="B120" s="9"/>
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
@@ -5382,7 +5423,7 @@
       <c r="AH120" s="9"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="58"/>
+      <c r="A121" s="59"/>
       <c r="B121" s="9"/>
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
@@ -5418,7 +5459,7 @@
       <c r="AH121" s="9"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="58"/>
+      <c r="A122" s="59"/>
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
@@ -5454,7 +5495,7 @@
       <c r="AH122" s="9"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="58"/>
+      <c r="A123" s="59"/>
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
@@ -5490,7 +5531,7 @@
       <c r="AH123" s="9"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="58"/>
+      <c r="A124" s="59"/>
       <c r="B124" s="9"/>
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
@@ -5526,7 +5567,7 @@
       <c r="AH124" s="9"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="58"/>
+      <c r="A125" s="59"/>
       <c r="B125" s="9"/>
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
@@ -5562,7 +5603,7 @@
       <c r="AH125" s="9"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="58"/>
+      <c r="A126" s="59"/>
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
@@ -5598,7 +5639,7 @@
       <c r="AH126" s="9"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="58"/>
+      <c r="A127" s="59"/>
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
@@ -5634,7 +5675,7 @@
       <c r="AH127" s="9"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="58"/>
+      <c r="A128" s="59"/>
       <c r="B128" s="9"/>
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
@@ -5670,7 +5711,7 @@
       <c r="AH128" s="9"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="58"/>
+      <c r="A129" s="59"/>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
       <c r="D129" s="9"/>
@@ -5706,7 +5747,7 @@
       <c r="AH129" s="9"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="58"/>
+      <c r="A130" s="59"/>
       <c r="B130" s="9"/>
       <c r="C130" s="9"/>
       <c r="D130" s="9"/>
@@ -5742,7 +5783,7 @@
       <c r="AH130" s="9"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="58"/>
+      <c r="A131" s="59"/>
       <c r="B131" s="9"/>
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
@@ -5778,7 +5819,7 @@
       <c r="AH131" s="9"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="58"/>
+      <c r="A132" s="59"/>
       <c r="B132" s="9"/>
       <c r="C132" s="9"/>
       <c r="D132" s="9"/>
@@ -5814,7 +5855,7 @@
       <c r="AH132" s="9"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="58"/>
+      <c r="A133" s="59"/>
       <c r="B133" s="9"/>
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
@@ -5850,7 +5891,7 @@
       <c r="AH133" s="9"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="58"/>
+      <c r="A134" s="59"/>
       <c r="B134" s="9"/>
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
@@ -5886,7 +5927,7 @@
       <c r="AH134" s="9"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="58"/>
+      <c r="A135" s="59"/>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
@@ -5922,7 +5963,7 @@
       <c r="AH135" s="9"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="58"/>
+      <c r="A136" s="59"/>
       <c r="B136" s="9"/>
       <c r="C136" s="9"/>
       <c r="D136" s="9"/>
@@ -5958,7 +5999,7 @@
       <c r="AH136" s="9"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="58"/>
+      <c r="A137" s="59"/>
       <c r="B137" s="9"/>
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
@@ -5994,7 +6035,7 @@
       <c r="AH137" s="9"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="58"/>
+      <c r="A138" s="59"/>
       <c r="B138" s="9"/>
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
@@ -6030,7 +6071,7 @@
       <c r="AH138" s="9"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="58"/>
+      <c r="A139" s="59"/>
       <c r="B139" s="9"/>
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
@@ -6066,7 +6107,7 @@
       <c r="AH139" s="9"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="58"/>
+      <c r="A140" s="59"/>
       <c r="B140" s="9"/>
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
@@ -6102,7 +6143,7 @@
       <c r="AH140" s="9"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="58"/>
+      <c r="A141" s="59"/>
       <c r="B141" s="9"/>
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
@@ -6138,7 +6179,7 @@
       <c r="AH141" s="9"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="58"/>
+      <c r="A142" s="59"/>
       <c r="B142" s="9"/>
       <c r="C142" s="9"/>
       <c r="D142" s="9"/>
@@ -6174,7 +6215,7 @@
       <c r="AH142" s="9"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="58"/>
+      <c r="A143" s="59"/>
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
       <c r="D143" s="9"/>
@@ -6210,7 +6251,7 @@
       <c r="AH143" s="9"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="58"/>
+      <c r="A144" s="59"/>
       <c r="B144" s="9"/>
       <c r="C144" s="9"/>
       <c r="D144" s="9"/>
@@ -6246,7 +6287,7 @@
       <c r="AH144" s="9"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="58"/>
+      <c r="A145" s="59"/>
       <c r="B145" s="9"/>
       <c r="C145" s="9"/>
       <c r="D145" s="9"/>
@@ -6282,7 +6323,7 @@
       <c r="AH145" s="9"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="58"/>
+      <c r="A146" s="59"/>
       <c r="B146" s="9"/>
       <c r="C146" s="9"/>
       <c r="D146" s="9"/>
@@ -6318,7 +6359,7 @@
       <c r="AH146" s="9"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="58"/>
+      <c r="A147" s="59"/>
       <c r="B147" s="9"/>
       <c r="C147" s="9"/>
       <c r="D147" s="9"/>
@@ -6354,7 +6395,7 @@
       <c r="AH147" s="9"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="58"/>
+      <c r="A148" s="59"/>
       <c r="B148" s="9"/>
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
@@ -6390,7 +6431,7 @@
       <c r="AH148" s="9"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="58"/>
+      <c r="A149" s="59"/>
       <c r="B149" s="9"/>
       <c r="C149" s="9"/>
       <c r="D149" s="9"/>
@@ -6426,7 +6467,7 @@
       <c r="AH149" s="9"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="58"/>
+      <c r="A150" s="59"/>
       <c r="B150" s="9"/>
       <c r="C150" s="9"/>
       <c r="D150" s="9"/>
@@ -6462,7 +6503,7 @@
       <c r="AH150" s="9"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="58"/>
+      <c r="A151" s="59"/>
       <c r="B151" s="9"/>
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
@@ -6498,7 +6539,7 @@
       <c r="AH151" s="9"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="58"/>
+      <c r="A152" s="59"/>
       <c r="B152" s="9"/>
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
@@ -6534,7 +6575,7 @@
       <c r="AH152" s="9"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="58"/>
+      <c r="A153" s="59"/>
       <c r="B153" s="9"/>
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
@@ -6570,7 +6611,7 @@
       <c r="AH153" s="9"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="58"/>
+      <c r="A154" s="59"/>
       <c r="B154" s="9"/>
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
@@ -6606,7 +6647,7 @@
       <c r="AH154" s="9"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="58"/>
+      <c r="A155" s="59"/>
       <c r="B155" s="9"/>
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
@@ -6642,7 +6683,7 @@
       <c r="AH155" s="9"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="58"/>
+      <c r="A156" s="59"/>
       <c r="B156" s="9"/>
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
@@ -6678,7 +6719,7 @@
       <c r="AH156" s="9"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="58"/>
+      <c r="A157" s="59"/>
       <c r="B157" s="9"/>
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
@@ -6714,7 +6755,7 @@
       <c r="AH157" s="9"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="58"/>
+      <c r="A158" s="59"/>
       <c r="B158" s="9"/>
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
@@ -6750,7 +6791,7 @@
       <c r="AH158" s="9"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="58"/>
+      <c r="A159" s="59"/>
       <c r="B159" s="9"/>
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
@@ -6786,7 +6827,7 @@
       <c r="AH159" s="9"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="58"/>
+      <c r="A160" s="59"/>
       <c r="B160" s="9"/>
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
@@ -6822,7 +6863,7 @@
       <c r="AH160" s="9"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="58"/>
+      <c r="A161" s="59"/>
       <c r="B161" s="9"/>
       <c r="C161" s="9"/>
       <c r="D161" s="9"/>
@@ -6858,7 +6899,7 @@
       <c r="AH161" s="9"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="58"/>
+      <c r="A162" s="59"/>
       <c r="B162" s="9"/>
       <c r="C162" s="9"/>
       <c r="D162" s="9"/>
@@ -6894,7 +6935,7 @@
       <c r="AH162" s="9"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="58"/>
+      <c r="A163" s="59"/>
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
@@ -6930,7 +6971,7 @@
       <c r="AH163" s="9"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="58"/>
+      <c r="A164" s="59"/>
       <c r="B164" s="9"/>
       <c r="C164" s="9"/>
       <c r="D164" s="9"/>
@@ -6966,7 +7007,7 @@
       <c r="AH164" s="9"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="58"/>
+      <c r="A165" s="59"/>
       <c r="B165" s="9"/>
       <c r="C165" s="9"/>
       <c r="D165" s="9"/>
@@ -7002,7 +7043,7 @@
       <c r="AH165" s="9"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="58"/>
+      <c r="A166" s="59"/>
       <c r="B166" s="9"/>
       <c r="C166" s="9"/>
       <c r="D166" s="9"/>
@@ -7038,7 +7079,7 @@
       <c r="AH166" s="9"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="58"/>
+      <c r="A167" s="59"/>
       <c r="B167" s="9"/>
       <c r="C167" s="9"/>
       <c r="D167" s="9"/>
@@ -7074,7 +7115,7 @@
       <c r="AH167" s="9"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="58"/>
+      <c r="A168" s="59"/>
       <c r="B168" s="9"/>
       <c r="C168" s="9"/>
       <c r="D168" s="9"/>
@@ -7110,7 +7151,7 @@
       <c r="AH168" s="9"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="58"/>
+      <c r="A169" s="59"/>
       <c r="B169" s="9"/>
       <c r="C169" s="9"/>
       <c r="D169" s="9"/>
@@ -7146,7 +7187,7 @@
       <c r="AH169" s="9"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="58"/>
+      <c r="A170" s="59"/>
       <c r="B170" s="9"/>
       <c r="C170" s="9"/>
       <c r="D170" s="9"/>
@@ -7182,7 +7223,7 @@
       <c r="AH170" s="9"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="58"/>
+      <c r="A171" s="59"/>
       <c r="B171" s="9"/>
       <c r="C171" s="9"/>
       <c r="D171" s="9"/>
@@ -7218,7 +7259,7 @@
       <c r="AH171" s="9"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="58"/>
+      <c r="A172" s="59"/>
       <c r="B172" s="9"/>
       <c r="C172" s="9"/>
       <c r="D172" s="9"/>
@@ -7254,7 +7295,7 @@
       <c r="AH172" s="9"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="58"/>
+      <c r="A173" s="59"/>
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
       <c r="D173" s="9"/>
@@ -7290,7 +7331,7 @@
       <c r="AH173" s="9"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="58"/>
+      <c r="A174" s="59"/>
       <c r="B174" s="9"/>
       <c r="C174" s="9"/>
       <c r="D174" s="9"/>
@@ -7326,7 +7367,7 @@
       <c r="AH174" s="9"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="58"/>
+      <c r="A175" s="59"/>
       <c r="B175" s="9"/>
       <c r="C175" s="9"/>
       <c r="D175" s="9"/>
@@ -7362,7 +7403,7 @@
       <c r="AH175" s="9"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="58"/>
+      <c r="A176" s="59"/>
       <c r="B176" s="9"/>
       <c r="C176" s="9"/>
       <c r="D176" s="9"/>
@@ -7398,7 +7439,7 @@
       <c r="AH176" s="9"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="58"/>
+      <c r="A177" s="59"/>
       <c r="B177" s="9"/>
       <c r="C177" s="9"/>
       <c r="D177" s="9"/>
@@ -7434,7 +7475,7 @@
       <c r="AH177" s="9"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="58"/>
+      <c r="A178" s="59"/>
       <c r="B178" s="9"/>
       <c r="C178" s="9"/>
       <c r="D178" s="9"/>
@@ -7470,7 +7511,7 @@
       <c r="AH178" s="9"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="58"/>
+      <c r="A179" s="59"/>
       <c r="B179" s="9"/>
       <c r="C179" s="9"/>
       <c r="D179" s="9"/>
@@ -7506,7 +7547,7 @@
       <c r="AH179" s="9"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="58"/>
+      <c r="A180" s="59"/>
       <c r="B180" s="9"/>
       <c r="C180" s="9"/>
       <c r="D180" s="9"/>
@@ -7542,7 +7583,7 @@
       <c r="AH180" s="9"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="58"/>
+      <c r="A181" s="59"/>
       <c r="B181" s="9"/>
       <c r="C181" s="9"/>
       <c r="D181" s="9"/>
@@ -7578,7 +7619,7 @@
       <c r="AH181" s="9"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="58"/>
+      <c r="A182" s="59"/>
       <c r="B182" s="9"/>
       <c r="C182" s="9"/>
       <c r="D182" s="9"/>
@@ -7614,7 +7655,7 @@
       <c r="AH182" s="9"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="58"/>
+      <c r="A183" s="59"/>
       <c r="B183" s="9"/>
       <c r="C183" s="9"/>
       <c r="D183" s="9"/>
@@ -7650,7 +7691,7 @@
       <c r="AH183" s="9"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="58"/>
+      <c r="A184" s="59"/>
       <c r="B184" s="9"/>
       <c r="C184" s="9"/>
       <c r="D184" s="9"/>
@@ -7686,7 +7727,7 @@
       <c r="AH184" s="9"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="58"/>
+      <c r="A185" s="59"/>
       <c r="B185" s="9"/>
       <c r="C185" s="9"/>
       <c r="D185" s="9"/>
@@ -7722,7 +7763,7 @@
       <c r="AH185" s="9"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="58"/>
+      <c r="A186" s="59"/>
       <c r="B186" s="9"/>
       <c r="C186" s="9"/>
       <c r="D186" s="9"/>
@@ -7758,7 +7799,7 @@
       <c r="AH186" s="9"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="58"/>
+      <c r="A187" s="59"/>
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
       <c r="D187" s="9"/>
@@ -7794,7 +7835,7 @@
       <c r="AH187" s="9"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="58"/>
+      <c r="A188" s="59"/>
       <c r="B188" s="9"/>
       <c r="C188" s="9"/>
       <c r="D188" s="9"/>
@@ -7830,7 +7871,7 @@
       <c r="AH188" s="9"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="58"/>
+      <c r="A189" s="59"/>
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
       <c r="D189" s="9"/>
@@ -7866,7 +7907,7 @@
       <c r="AH189" s="9"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="58"/>
+      <c r="A190" s="59"/>
       <c r="B190" s="9"/>
       <c r="C190" s="9"/>
       <c r="D190" s="9"/>
@@ -7902,7 +7943,7 @@
       <c r="AH190" s="9"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="58"/>
+      <c r="A191" s="59"/>
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
       <c r="D191" s="9"/>
@@ -7938,7 +7979,7 @@
       <c r="AH191" s="9"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="58"/>
+      <c r="A192" s="59"/>
       <c r="B192" s="9"/>
       <c r="C192" s="9"/>
       <c r="D192" s="9"/>
@@ -7974,7 +8015,7 @@
       <c r="AH192" s="9"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="58"/>
+      <c r="A193" s="59"/>
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
       <c r="D193" s="9"/>
@@ -8010,7 +8051,7 @@
       <c r="AH193" s="9"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="58"/>
+      <c r="A194" s="59"/>
       <c r="B194" s="9"/>
       <c r="C194" s="9"/>
       <c r="D194" s="9"/>
@@ -8046,7 +8087,7 @@
       <c r="AH194" s="9"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="58"/>
+      <c r="A195" s="59"/>
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
       <c r="D195" s="9"/>
@@ -8082,7 +8123,7 @@
       <c r="AH195" s="9"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="58"/>
+      <c r="A196" s="59"/>
       <c r="B196" s="9"/>
       <c r="C196" s="9"/>
       <c r="D196" s="9"/>
@@ -8118,7 +8159,7 @@
       <c r="AH196" s="9"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="58"/>
+      <c r="A197" s="59"/>
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
       <c r="D197" s="9"/>
@@ -8154,7 +8195,7 @@
       <c r="AH197" s="9"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="58"/>
+      <c r="A198" s="59"/>
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
       <c r="D198" s="9"/>
@@ -8190,7 +8231,7 @@
       <c r="AH198" s="9"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="58"/>
+      <c r="A199" s="59"/>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
       <c r="D199" s="9"/>
@@ -8226,7 +8267,7 @@
       <c r="AH199" s="9"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="58"/>
+      <c r="A200" s="59"/>
       <c r="B200" s="9"/>
       <c r="C200" s="9"/>
       <c r="D200" s="9"/>
@@ -8262,7 +8303,7 @@
       <c r="AH200" s="9"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="58"/>
+      <c r="A201" s="59"/>
       <c r="B201" s="9"/>
       <c r="C201" s="9"/>
       <c r="D201" s="9"/>
@@ -8298,7 +8339,7 @@
       <c r="AH201" s="9"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="58"/>
+      <c r="A202" s="59"/>
       <c r="B202" s="9"/>
       <c r="C202" s="9"/>
       <c r="D202" s="9"/>
@@ -8334,7 +8375,7 @@
       <c r="AH202" s="9"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="58"/>
+      <c r="A203" s="59"/>
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
       <c r="D203" s="9"/>
@@ -8370,7 +8411,7 @@
       <c r="AH203" s="9"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="58"/>
+      <c r="A204" s="59"/>
       <c r="B204" s="9"/>
       <c r="C204" s="9"/>
       <c r="D204" s="9"/>
@@ -8406,7 +8447,7 @@
       <c r="AH204" s="9"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="58"/>
+      <c r="A205" s="59"/>
       <c r="B205" s="9"/>
       <c r="C205" s="9"/>
       <c r="D205" s="9"/>
@@ -8442,7 +8483,7 @@
       <c r="AH205" s="9"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="58"/>
+      <c r="A206" s="59"/>
       <c r="B206" s="9"/>
       <c r="C206" s="9"/>
       <c r="D206" s="9"/>
@@ -8478,7 +8519,7 @@
       <c r="AH206" s="9"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="58"/>
+      <c r="A207" s="59"/>
       <c r="B207" s="9"/>
       <c r="C207" s="9"/>
       <c r="D207" s="9"/>
@@ -8514,7 +8555,7 @@
       <c r="AH207" s="9"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="58"/>
+      <c r="A208" s="59"/>
       <c r="B208" s="9"/>
       <c r="C208" s="9"/>
       <c r="D208" s="9"/>
@@ -8550,7 +8591,7 @@
       <c r="AH208" s="9"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="58"/>
+      <c r="A209" s="59"/>
       <c r="B209" s="9"/>
       <c r="C209" s="9"/>
       <c r="D209" s="9"/>
@@ -8586,7 +8627,7 @@
       <c r="AH209" s="9"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="58"/>
+      <c r="A210" s="59"/>
       <c r="B210" s="9"/>
       <c r="C210" s="9"/>
       <c r="D210" s="9"/>
@@ -8622,7 +8663,7 @@
       <c r="AH210" s="9"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="58"/>
+      <c r="A211" s="59"/>
       <c r="B211" s="9"/>
       <c r="C211" s="9"/>
       <c r="D211" s="9"/>
@@ -8658,7 +8699,7 @@
       <c r="AH211" s="9"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="58"/>
+      <c r="A212" s="59"/>
       <c r="B212" s="9"/>
       <c r="C212" s="9"/>
       <c r="D212" s="9"/>
@@ -8694,7 +8735,7 @@
       <c r="AH212" s="9"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="58"/>
+      <c r="A213" s="59"/>
       <c r="B213" s="9"/>
       <c r="C213" s="9"/>
       <c r="D213" s="9"/>
@@ -8730,7 +8771,7 @@
       <c r="AH213" s="9"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="58"/>
+      <c r="A214" s="59"/>
       <c r="B214" s="9"/>
       <c r="C214" s="9"/>
       <c r="D214" s="9"/>
@@ -8766,7 +8807,7 @@
       <c r="AH214" s="9"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="58"/>
+      <c r="A215" s="59"/>
       <c r="B215" s="9"/>
       <c r="C215" s="9"/>
       <c r="D215" s="9"/>
@@ -8802,7 +8843,7 @@
       <c r="AH215" s="9"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="58"/>
+      <c r="A216" s="59"/>
       <c r="B216" s="9"/>
       <c r="C216" s="9"/>
       <c r="D216" s="9"/>
@@ -8838,7 +8879,7 @@
       <c r="AH216" s="9"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="58"/>
+      <c r="A217" s="59"/>
       <c r="B217" s="9"/>
       <c r="C217" s="9"/>
       <c r="D217" s="9"/>
@@ -8874,7 +8915,7 @@
       <c r="AH217" s="9"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="58"/>
+      <c r="A218" s="59"/>
       <c r="B218" s="9"/>
       <c r="C218" s="9"/>
       <c r="D218" s="9"/>
@@ -8910,7 +8951,7 @@
       <c r="AH218" s="9"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="58"/>
+      <c r="A219" s="59"/>
       <c r="B219" s="9"/>
       <c r="C219" s="9"/>
       <c r="D219" s="9"/>
@@ -8946,7 +8987,7 @@
       <c r="AH219" s="9"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="58"/>
+      <c r="A220" s="59"/>
       <c r="B220" s="9"/>
       <c r="C220" s="9"/>
       <c r="D220" s="9"/>
@@ -8982,7 +9023,7 @@
       <c r="AH220" s="9"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="58"/>
+      <c r="A221" s="59"/>
       <c r="B221" s="9"/>
       <c r="C221" s="9"/>
       <c r="D221" s="9"/>
@@ -9018,7 +9059,7 @@
       <c r="AH221" s="9"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="58"/>
+      <c r="A222" s="59"/>
       <c r="B222" s="9"/>
       <c r="C222" s="9"/>
       <c r="D222" s="9"/>
@@ -9054,7 +9095,7 @@
       <c r="AH222" s="9"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="58"/>
+      <c r="A223" s="59"/>
       <c r="B223" s="9"/>
       <c r="C223" s="9"/>
       <c r="D223" s="9"/>
@@ -9090,7 +9131,7 @@
       <c r="AH223" s="9"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="58"/>
+      <c r="A224" s="59"/>
       <c r="B224" s="9"/>
       <c r="C224" s="9"/>
       <c r="D224" s="9"/>
@@ -9126,7 +9167,7 @@
       <c r="AH224" s="9"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="58"/>
+      <c r="A225" s="59"/>
       <c r="B225" s="9"/>
       <c r="C225" s="9"/>
       <c r="D225" s="9"/>
@@ -9162,7 +9203,7 @@
       <c r="AH225" s="9"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="58"/>
+      <c r="A226" s="59"/>
       <c r="B226" s="9"/>
       <c r="C226" s="9"/>
       <c r="D226" s="9"/>
@@ -9198,7 +9239,7 @@
       <c r="AH226" s="9"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="58"/>
+      <c r="A227" s="59"/>
       <c r="B227" s="9"/>
       <c r="C227" s="9"/>
       <c r="D227" s="9"/>
@@ -9234,7 +9275,7 @@
       <c r="AH227" s="9"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="58"/>
+      <c r="A228" s="59"/>
       <c r="B228" s="9"/>
       <c r="C228" s="9"/>
       <c r="D228" s="9"/>
@@ -9270,7 +9311,7 @@
       <c r="AH228" s="9"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="58"/>
+      <c r="A229" s="59"/>
       <c r="B229" s="9"/>
       <c r="C229" s="9"/>
       <c r="D229" s="9"/>
@@ -9306,7 +9347,7 @@
       <c r="AH229" s="9"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="58"/>
+      <c r="A230" s="59"/>
       <c r="B230" s="9"/>
       <c r="C230" s="9"/>
       <c r="D230" s="9"/>
@@ -9342,7 +9383,7 @@
       <c r="AH230" s="9"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="58"/>
+      <c r="A231" s="59"/>
       <c r="B231" s="9"/>
       <c r="C231" s="9"/>
       <c r="D231" s="9"/>
@@ -9378,7 +9419,7 @@
       <c r="AH231" s="9"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="58"/>
+      <c r="A232" s="59"/>
       <c r="B232" s="9"/>
       <c r="C232" s="9"/>
       <c r="D232" s="9"/>
@@ -9414,7 +9455,7 @@
       <c r="AH232" s="9"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="58"/>
+      <c r="A233" s="59"/>
       <c r="B233" s="9"/>
       <c r="C233" s="9"/>
       <c r="D233" s="9"/>
@@ -9450,7 +9491,7 @@
       <c r="AH233" s="9"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="58"/>
+      <c r="A234" s="59"/>
       <c r="B234" s="9"/>
       <c r="C234" s="9"/>
       <c r="D234" s="9"/>
@@ -9486,7 +9527,7 @@
       <c r="AH234" s="9"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="58"/>
+      <c r="A235" s="59"/>
       <c r="B235" s="9"/>
       <c r="C235" s="9"/>
       <c r="D235" s="9"/>
@@ -9522,7 +9563,7 @@
       <c r="AH235" s="9"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="58"/>
+      <c r="A236" s="59"/>
       <c r="B236" s="9"/>
       <c r="C236" s="9"/>
       <c r="D236" s="9"/>
@@ -9558,7 +9599,7 @@
       <c r="AH236" s="9"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="58"/>
+      <c r="A237" s="59"/>
       <c r="B237" s="9"/>
       <c r="C237" s="9"/>
       <c r="D237" s="9"/>
@@ -9594,7 +9635,7 @@
       <c r="AH237" s="9"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="58"/>
+      <c r="A238" s="59"/>
       <c r="B238" s="9"/>
       <c r="C238" s="9"/>
       <c r="D238" s="9"/>
@@ -9630,7 +9671,7 @@
       <c r="AH238" s="9"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="58"/>
+      <c r="A239" s="59"/>
       <c r="B239" s="9"/>
       <c r="C239" s="9"/>
       <c r="D239" s="9"/>
@@ -9666,7 +9707,7 @@
       <c r="AH239" s="9"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="58"/>
+      <c r="A240" s="59"/>
       <c r="B240" s="9"/>
       <c r="C240" s="9"/>
       <c r="D240" s="9"/>
@@ -9702,7 +9743,7 @@
       <c r="AH240" s="9"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="58"/>
+      <c r="A241" s="59"/>
       <c r="B241" s="9"/>
       <c r="C241" s="9"/>
       <c r="D241" s="9"/>
@@ -9738,7 +9779,7 @@
       <c r="AH241" s="9"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="58"/>
+      <c r="A242" s="59"/>
       <c r="B242" s="9"/>
       <c r="C242" s="9"/>
       <c r="D242" s="9"/>
@@ -9774,7 +9815,7 @@
       <c r="AH242" s="9"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="58"/>
+      <c r="A243" s="59"/>
       <c r="B243" s="9"/>
       <c r="C243" s="9"/>
       <c r="D243" s="9"/>
@@ -9810,7 +9851,7 @@
       <c r="AH243" s="9"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="58"/>
+      <c r="A244" s="59"/>
       <c r="B244" s="9"/>
       <c r="C244" s="9"/>
       <c r="D244" s="9"/>
@@ -9846,7 +9887,7 @@
       <c r="AH244" s="9"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="58"/>
+      <c r="A245" s="59"/>
       <c r="B245" s="9"/>
       <c r="C245" s="9"/>
       <c r="D245" s="9"/>
@@ -9882,7 +9923,7 @@
       <c r="AH245" s="9"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="58"/>
+      <c r="A246" s="59"/>
       <c r="B246" s="9"/>
       <c r="C246" s="9"/>
       <c r="D246" s="9"/>
@@ -9918,7 +9959,7 @@
       <c r="AH246" s="9"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="58"/>
+      <c r="A247" s="59"/>
       <c r="B247" s="9"/>
       <c r="C247" s="9"/>
       <c r="D247" s="9"/>
@@ -9954,7 +9995,7 @@
       <c r="AH247" s="9"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="58"/>
+      <c r="A248" s="59"/>
       <c r="B248" s="9"/>
       <c r="C248" s="9"/>
       <c r="D248" s="9"/>
@@ -9990,7 +10031,7 @@
       <c r="AH248" s="9"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="58"/>
+      <c r="A249" s="59"/>
       <c r="B249" s="9"/>
       <c r="C249" s="9"/>
       <c r="D249" s="9"/>
@@ -10026,7 +10067,7 @@
       <c r="AH249" s="9"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="58"/>
+      <c r="A250" s="59"/>
       <c r="B250" s="9"/>
       <c r="C250" s="9"/>
       <c r="D250" s="9"/>
@@ -10062,7 +10103,7 @@
       <c r="AH250" s="9"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="58"/>
+      <c r="A251" s="59"/>
       <c r="B251" s="9"/>
       <c r="C251" s="9"/>
       <c r="D251" s="9"/>
@@ -10098,7 +10139,7 @@
       <c r="AH251" s="9"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="58"/>
+      <c r="A252" s="59"/>
       <c r="B252" s="9"/>
       <c r="C252" s="9"/>
       <c r="D252" s="9"/>
@@ -10134,7 +10175,7 @@
       <c r="AH252" s="9"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="58"/>
+      <c r="A253" s="59"/>
       <c r="B253" s="9"/>
       <c r="C253" s="9"/>
       <c r="D253" s="9"/>
@@ -10170,7 +10211,7 @@
       <c r="AH253" s="9"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="58"/>
+      <c r="A254" s="59"/>
       <c r="B254" s="9"/>
       <c r="C254" s="9"/>
       <c r="D254" s="9"/>
@@ -10206,7 +10247,7 @@
       <c r="AH254" s="9"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="58"/>
+      <c r="A255" s="59"/>
       <c r="B255" s="9"/>
       <c r="C255" s="9"/>
       <c r="D255" s="9"/>
@@ -10242,7 +10283,7 @@
       <c r="AH255" s="9"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="58"/>
+      <c r="A256" s="59"/>
       <c r="B256" s="9"/>
       <c r="C256" s="9"/>
       <c r="D256" s="9"/>
@@ -10278,7 +10319,7 @@
       <c r="AH256" s="9"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="58"/>
+      <c r="A257" s="59"/>
       <c r="B257" s="9"/>
       <c r="C257" s="9"/>
       <c r="D257" s="9"/>
@@ -10314,7 +10355,7 @@
       <c r="AH257" s="9"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="58"/>
+      <c r="A258" s="59"/>
       <c r="B258" s="9"/>
       <c r="C258" s="9"/>
       <c r="D258" s="9"/>
@@ -10350,7 +10391,7 @@
       <c r="AH258" s="9"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="58"/>
+      <c r="A259" s="59"/>
       <c r="B259" s="9"/>
       <c r="C259" s="9"/>
       <c r="D259" s="9"/>
@@ -10386,7 +10427,7 @@
       <c r="AH259" s="9"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="58"/>
+      <c r="A260" s="59"/>
       <c r="B260" s="9"/>
       <c r="C260" s="9"/>
       <c r="D260" s="9"/>
@@ -10422,7 +10463,7 @@
       <c r="AH260" s="9"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="58"/>
+      <c r="A261" s="59"/>
       <c r="B261" s="9"/>
       <c r="C261" s="9"/>
       <c r="D261" s="9"/>
@@ -10458,7 +10499,7 @@
       <c r="AH261" s="9"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="58"/>
+      <c r="A262" s="59"/>
       <c r="B262" s="9"/>
       <c r="C262" s="9"/>
       <c r="D262" s="9"/>
@@ -11232,7 +11273,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="314">
+  <mergeCells count="339">
     <mergeCell ref="H13:H17"/>
     <mergeCell ref="I13:I17"/>
     <mergeCell ref="J13:J17"/>
@@ -11339,6 +11380,35 @@
     <mergeCell ref="F80:F82"/>
     <mergeCell ref="G80:G82"/>
     <mergeCell ref="H80:H82"/>
+    <mergeCell ref="I85:I89"/>
+    <mergeCell ref="J85:J89"/>
+    <mergeCell ref="K85:K87"/>
+    <mergeCell ref="L85:L89"/>
+    <mergeCell ref="M85:M89"/>
+    <mergeCell ref="N85:N89"/>
+    <mergeCell ref="O85:O89"/>
+    <mergeCell ref="K88:K89"/>
+    <mergeCell ref="A85:A89"/>
+    <mergeCell ref="B85:B89"/>
+    <mergeCell ref="C85:C89"/>
+    <mergeCell ref="E85:E89"/>
+    <mergeCell ref="F85:F89"/>
+    <mergeCell ref="G85:G89"/>
+    <mergeCell ref="H85:H89"/>
+    <mergeCell ref="I92:I95"/>
+    <mergeCell ref="J92:J95"/>
+    <mergeCell ref="K92:K95"/>
+    <mergeCell ref="L92:L95"/>
+    <mergeCell ref="M92:M95"/>
+    <mergeCell ref="N92:N95"/>
+    <mergeCell ref="O92:O95"/>
+    <mergeCell ref="A92:A95"/>
+    <mergeCell ref="B92:B95"/>
+    <mergeCell ref="D92:D95"/>
+    <mergeCell ref="E92:E95"/>
+    <mergeCell ref="F92:F95"/>
+    <mergeCell ref="G92:G95"/>
+    <mergeCell ref="H92:H95"/>
     <mergeCell ref="H71:H73"/>
     <mergeCell ref="I71:I73"/>
     <mergeCell ref="J71:J73"/>
@@ -11378,21 +11448,17 @@
     <mergeCell ref="I77:I79"/>
     <mergeCell ref="J77:J79"/>
     <mergeCell ref="K77:K79"/>
-    <mergeCell ref="I85:I89"/>
-    <mergeCell ref="J85:J89"/>
-    <mergeCell ref="L85:L89"/>
-    <mergeCell ref="M85:M89"/>
-    <mergeCell ref="N85:N89"/>
-    <mergeCell ref="O85:O89"/>
-    <mergeCell ref="K85:K87"/>
-    <mergeCell ref="K88:K89"/>
-    <mergeCell ref="A85:A89"/>
-    <mergeCell ref="B85:B89"/>
-    <mergeCell ref="C85:C89"/>
-    <mergeCell ref="E85:E89"/>
-    <mergeCell ref="F85:F89"/>
-    <mergeCell ref="G85:G89"/>
-    <mergeCell ref="H85:H89"/>
+    <mergeCell ref="L96:L97"/>
+    <mergeCell ref="M96:M97"/>
+    <mergeCell ref="N96:N97"/>
+    <mergeCell ref="O96:O97"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="E96:E97"/>
+    <mergeCell ref="J96:J97"/>
+    <mergeCell ref="K96:K97"/>
     <mergeCell ref="H22:H26"/>
     <mergeCell ref="I22:I26"/>
     <mergeCell ref="J22:J26"/>
@@ -11570,58 +11636,58 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="59" t="s">
-        <v>134</v>
-      </c>
-      <c r="B2" s="59" t="s">
-        <v>135</v>
-      </c>
-      <c r="C2" s="59" t="s">
-        <v>136</v>
+      <c r="A2" s="60" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="59" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="59" t="s">
-        <v>139</v>
+      <c r="A3" s="60" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="59" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="59" t="s">
+      <c r="A4" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="59" t="s">
-        <v>141</v>
+      <c r="C4" s="60" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="59" t="s">
-        <v>144</v>
+      <c r="A5" s="60" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="59" t="s">
-        <v>145</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>147</v>
+      <c r="A6" s="60" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="60" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>

--- a/Grade2-Homeworks.xlsx
+++ b/Grade2-Homeworks.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="161">
   <si>
     <t>Date</t>
   </si>
@@ -565,7 +565,7 @@
     <t xml:space="preserve">Prepare your own CV &amp; resume in 'markdown' </t>
   </si>
   <si>
-    <t xml:space="preserve"> fix Copy tracing book (latex) - show it to your parents; Add missing letters; Complete copy tracing</t>
+    <t>Fix Copy tracing book (latex) - show it to your parents; Add missing letters; Complete copy tracing</t>
   </si>
   <si>
     <t xml:space="preserve">Correct these songs, breakdown etc. and practice singing together  :
@@ -591,6 +591,15 @@
   </si>
   <si>
     <t>Run the python example with different number of cores from 1 to 4 and note how the time changes (Inverse proportion - Sequential &amp; parallel work )</t>
+  </si>
+  <si>
+    <t>Complete previous HW</t>
+  </si>
+  <si>
+    <t>HW: Study AI Summaries of all the chapters(Mahavira story)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Study the following: Listen to + read full puja speech (Shri Mataji's Speech on Mahavira puja 1991; AI Summary and comparison with text chapters)</t>
   </si>
   <si>
     <t>Monday</t>
@@ -835,7 +844,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -986,13 +995,16 @@
     <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -4351,7 +4363,7 @@
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
       <c r="D91" s="6"/>
-      <c r="E91" s="56" t="s">
+      <c r="E91" s="57" t="s">
         <v>136</v>
       </c>
       <c r="F91" s="6"/>
@@ -4391,7 +4403,7 @@
         <v>46091.0</v>
       </c>
       <c r="B92" s="11"/>
-      <c r="C92" s="57" t="s">
+      <c r="C92" s="48" t="s">
         <v>138</v>
       </c>
       <c r="D92" s="11"/>
@@ -4428,7 +4440,7 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="27"/>
-      <c r="C93" s="54" t="s">
+      <c r="C93" s="49" t="s">
         <v>139</v>
       </c>
       <c r="O93" s="22"/>
@@ -4454,7 +4466,7 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="27"/>
-      <c r="C94" s="54" t="s">
+      <c r="C94" s="49" t="s">
         <v>140</v>
       </c>
       <c r="O94" s="22"/>
@@ -4527,7 +4539,7 @@
       <c r="F96" s="11"/>
       <c r="G96" s="11"/>
       <c r="H96" s="11"/>
-      <c r="I96" s="57" t="s">
+      <c r="I96" s="59" t="s">
         <v>142</v>
       </c>
       <c r="J96" s="11"/>
@@ -4595,21 +4607,25 @@
       <c r="AH97" s="9"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="59"/>
-      <c r="B98" s="9"/>
-      <c r="C98" s="9"/>
-      <c r="D98" s="9"/>
-      <c r="E98" s="9"/>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="9"/>
-      <c r="J98" s="9"/>
-      <c r="K98" s="9"/>
-      <c r="L98" s="9"/>
-      <c r="M98" s="9"/>
-      <c r="N98" s="9"/>
-      <c r="O98" s="9"/>
+      <c r="A98" s="47">
+        <v>46101.0</v>
+      </c>
+      <c r="B98" s="11"/>
+      <c r="C98" s="11"/>
+      <c r="D98" s="59" t="s">
+        <v>144</v>
+      </c>
+      <c r="E98" s="11"/>
+      <c r="F98" s="11"/>
+      <c r="G98" s="11"/>
+      <c r="H98" s="11"/>
+      <c r="I98" s="11"/>
+      <c r="J98" s="11"/>
+      <c r="K98" s="11"/>
+      <c r="L98" s="11"/>
+      <c r="M98" s="11"/>
+      <c r="N98" s="11"/>
+      <c r="O98" s="14"/>
       <c r="P98" s="9"/>
       <c r="Q98" s="4"/>
       <c r="R98" s="9"/>
@@ -4631,21 +4647,11 @@
       <c r="AH98" s="9"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="59"/>
-      <c r="B99" s="9"/>
-      <c r="C99" s="9"/>
-      <c r="D99" s="9"/>
-      <c r="E99" s="9"/>
-      <c r="F99" s="9"/>
-      <c r="G99" s="9"/>
-      <c r="H99" s="9"/>
-      <c r="I99" s="9"/>
-      <c r="J99" s="9"/>
-      <c r="K99" s="9"/>
-      <c r="L99" s="9"/>
-      <c r="M99" s="9"/>
-      <c r="N99" s="9"/>
-      <c r="O99" s="9"/>
+      <c r="A99" s="27"/>
+      <c r="D99" s="54" t="s">
+        <v>145</v>
+      </c>
+      <c r="O99" s="22"/>
       <c r="P99" s="9"/>
       <c r="Q99" s="4"/>
       <c r="R99" s="9"/>
@@ -4667,21 +4673,23 @@
       <c r="AH99" s="9"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="59"/>
-      <c r="B100" s="9"/>
-      <c r="C100" s="9"/>
-      <c r="D100" s="9"/>
-      <c r="E100" s="9"/>
-      <c r="F100" s="9"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="9"/>
-      <c r="I100" s="9"/>
-      <c r="J100" s="9"/>
-      <c r="K100" s="9"/>
-      <c r="L100" s="9"/>
-      <c r="M100" s="9"/>
-      <c r="N100" s="9"/>
-      <c r="O100" s="9"/>
+      <c r="A100" s="29"/>
+      <c r="B100" s="16"/>
+      <c r="C100" s="16"/>
+      <c r="D100" s="58" t="s">
+        <v>146</v>
+      </c>
+      <c r="E100" s="16"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="16"/>
+      <c r="H100" s="16"/>
+      <c r="I100" s="16"/>
+      <c r="J100" s="16"/>
+      <c r="K100" s="16"/>
+      <c r="L100" s="16"/>
+      <c r="M100" s="16"/>
+      <c r="N100" s="16"/>
+      <c r="O100" s="18"/>
       <c r="P100" s="9"/>
       <c r="Q100" s="4"/>
       <c r="R100" s="9"/>
@@ -4703,7 +4711,7 @@
       <c r="AH100" s="9"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="59"/>
+      <c r="A101" s="60"/>
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
@@ -4739,7 +4747,7 @@
       <c r="AH101" s="9"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="59"/>
+      <c r="A102" s="60"/>
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
@@ -4775,7 +4783,7 @@
       <c r="AH102" s="9"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="59"/>
+      <c r="A103" s="60"/>
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
@@ -4811,7 +4819,7 @@
       <c r="AH103" s="9"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="59"/>
+      <c r="A104" s="60"/>
       <c r="B104" s="9"/>
       <c r="C104" s="9"/>
       <c r="D104" s="9"/>
@@ -4847,7 +4855,7 @@
       <c r="AH104" s="9"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="59"/>
+      <c r="A105" s="60"/>
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
       <c r="D105" s="9"/>
@@ -4883,7 +4891,7 @@
       <c r="AH105" s="9"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="59"/>
+      <c r="A106" s="60"/>
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
@@ -4919,7 +4927,7 @@
       <c r="AH106" s="9"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="59"/>
+      <c r="A107" s="60"/>
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
@@ -4955,7 +4963,7 @@
       <c r="AH107" s="9"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="59"/>
+      <c r="A108" s="60"/>
       <c r="B108" s="9"/>
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
@@ -4991,7 +4999,7 @@
       <c r="AH108" s="9"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="59"/>
+      <c r="A109" s="60"/>
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
@@ -5027,7 +5035,7 @@
       <c r="AH109" s="9"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="59"/>
+      <c r="A110" s="60"/>
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
@@ -5063,7 +5071,7 @@
       <c r="AH110" s="9"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="59"/>
+      <c r="A111" s="60"/>
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
@@ -5099,7 +5107,7 @@
       <c r="AH111" s="9"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="59"/>
+      <c r="A112" s="60"/>
       <c r="B112" s="9"/>
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
@@ -5135,7 +5143,7 @@
       <c r="AH112" s="9"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="59"/>
+      <c r="A113" s="60"/>
       <c r="B113" s="9"/>
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
@@ -5171,7 +5179,7 @@
       <c r="AH113" s="9"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="59"/>
+      <c r="A114" s="60"/>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
@@ -5207,7 +5215,7 @@
       <c r="AH114" s="9"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="59"/>
+      <c r="A115" s="60"/>
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
@@ -5243,7 +5251,7 @@
       <c r="AH115" s="9"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="59"/>
+      <c r="A116" s="60"/>
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
@@ -5279,7 +5287,7 @@
       <c r="AH116" s="9"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="59"/>
+      <c r="A117" s="60"/>
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
@@ -5315,7 +5323,7 @@
       <c r="AH117" s="9"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="59"/>
+      <c r="A118" s="60"/>
       <c r="B118" s="9"/>
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
@@ -5351,7 +5359,7 @@
       <c r="AH118" s="9"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="59"/>
+      <c r="A119" s="60"/>
       <c r="B119" s="9"/>
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
@@ -5387,7 +5395,7 @@
       <c r="AH119" s="9"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="59"/>
+      <c r="A120" s="60"/>
       <c r="B120" s="9"/>
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
@@ -5423,7 +5431,7 @@
       <c r="AH120" s="9"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="59"/>
+      <c r="A121" s="60"/>
       <c r="B121" s="9"/>
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
@@ -5459,7 +5467,7 @@
       <c r="AH121" s="9"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="59"/>
+      <c r="A122" s="60"/>
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
@@ -5495,7 +5503,7 @@
       <c r="AH122" s="9"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="59"/>
+      <c r="A123" s="60"/>
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
@@ -5531,7 +5539,7 @@
       <c r="AH123" s="9"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="59"/>
+      <c r="A124" s="60"/>
       <c r="B124" s="9"/>
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
@@ -5567,7 +5575,7 @@
       <c r="AH124" s="9"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="59"/>
+      <c r="A125" s="60"/>
       <c r="B125" s="9"/>
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
@@ -5603,7 +5611,7 @@
       <c r="AH125" s="9"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="59"/>
+      <c r="A126" s="60"/>
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
@@ -5639,7 +5647,7 @@
       <c r="AH126" s="9"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="59"/>
+      <c r="A127" s="60"/>
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
@@ -5675,7 +5683,7 @@
       <c r="AH127" s="9"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="59"/>
+      <c r="A128" s="60"/>
       <c r="B128" s="9"/>
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
@@ -5711,7 +5719,7 @@
       <c r="AH128" s="9"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="59"/>
+      <c r="A129" s="60"/>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
       <c r="D129" s="9"/>
@@ -5747,7 +5755,7 @@
       <c r="AH129" s="9"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="59"/>
+      <c r="A130" s="60"/>
       <c r="B130" s="9"/>
       <c r="C130" s="9"/>
       <c r="D130" s="9"/>
@@ -5783,7 +5791,7 @@
       <c r="AH130" s="9"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="59"/>
+      <c r="A131" s="60"/>
       <c r="B131" s="9"/>
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
@@ -5819,7 +5827,7 @@
       <c r="AH131" s="9"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="59"/>
+      <c r="A132" s="60"/>
       <c r="B132" s="9"/>
       <c r="C132" s="9"/>
       <c r="D132" s="9"/>
@@ -5855,7 +5863,7 @@
       <c r="AH132" s="9"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="59"/>
+      <c r="A133" s="60"/>
       <c r="B133" s="9"/>
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
@@ -5891,7 +5899,7 @@
       <c r="AH133" s="9"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="59"/>
+      <c r="A134" s="60"/>
       <c r="B134" s="9"/>
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
@@ -5927,7 +5935,7 @@
       <c r="AH134" s="9"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="59"/>
+      <c r="A135" s="60"/>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
@@ -5963,7 +5971,7 @@
       <c r="AH135" s="9"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="59"/>
+      <c r="A136" s="60"/>
       <c r="B136" s="9"/>
       <c r="C136" s="9"/>
       <c r="D136" s="9"/>
@@ -5999,7 +6007,7 @@
       <c r="AH136" s="9"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="59"/>
+      <c r="A137" s="60"/>
       <c r="B137" s="9"/>
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
@@ -6035,7 +6043,7 @@
       <c r="AH137" s="9"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="59"/>
+      <c r="A138" s="60"/>
       <c r="B138" s="9"/>
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
@@ -6071,7 +6079,7 @@
       <c r="AH138" s="9"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="59"/>
+      <c r="A139" s="60"/>
       <c r="B139" s="9"/>
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
@@ -6107,7 +6115,7 @@
       <c r="AH139" s="9"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="59"/>
+      <c r="A140" s="60"/>
       <c r="B140" s="9"/>
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
@@ -6143,7 +6151,7 @@
       <c r="AH140" s="9"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="59"/>
+      <c r="A141" s="60"/>
       <c r="B141" s="9"/>
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
@@ -6179,7 +6187,7 @@
       <c r="AH141" s="9"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="59"/>
+      <c r="A142" s="60"/>
       <c r="B142" s="9"/>
       <c r="C142" s="9"/>
       <c r="D142" s="9"/>
@@ -6215,7 +6223,7 @@
       <c r="AH142" s="9"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="59"/>
+      <c r="A143" s="60"/>
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
       <c r="D143" s="9"/>
@@ -6251,7 +6259,7 @@
       <c r="AH143" s="9"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="59"/>
+      <c r="A144" s="60"/>
       <c r="B144" s="9"/>
       <c r="C144" s="9"/>
       <c r="D144" s="9"/>
@@ -6287,7 +6295,7 @@
       <c r="AH144" s="9"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="59"/>
+      <c r="A145" s="60"/>
       <c r="B145" s="9"/>
       <c r="C145" s="9"/>
       <c r="D145" s="9"/>
@@ -6323,7 +6331,7 @@
       <c r="AH145" s="9"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="59"/>
+      <c r="A146" s="60"/>
       <c r="B146" s="9"/>
       <c r="C146" s="9"/>
       <c r="D146" s="9"/>
@@ -6359,7 +6367,7 @@
       <c r="AH146" s="9"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="59"/>
+      <c r="A147" s="60"/>
       <c r="B147" s="9"/>
       <c r="C147" s="9"/>
       <c r="D147" s="9"/>
@@ -6395,7 +6403,7 @@
       <c r="AH147" s="9"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="59"/>
+      <c r="A148" s="60"/>
       <c r="B148" s="9"/>
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
@@ -6431,7 +6439,7 @@
       <c r="AH148" s="9"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="59"/>
+      <c r="A149" s="60"/>
       <c r="B149" s="9"/>
       <c r="C149" s="9"/>
       <c r="D149" s="9"/>
@@ -6467,7 +6475,7 @@
       <c r="AH149" s="9"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="59"/>
+      <c r="A150" s="60"/>
       <c r="B150" s="9"/>
       <c r="C150" s="9"/>
       <c r="D150" s="9"/>
@@ -6503,7 +6511,7 @@
       <c r="AH150" s="9"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="59"/>
+      <c r="A151" s="60"/>
       <c r="B151" s="9"/>
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
@@ -6539,7 +6547,7 @@
       <c r="AH151" s="9"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="59"/>
+      <c r="A152" s="60"/>
       <c r="B152" s="9"/>
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
@@ -6575,7 +6583,7 @@
       <c r="AH152" s="9"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="59"/>
+      <c r="A153" s="60"/>
       <c r="B153" s="9"/>
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
@@ -6611,7 +6619,7 @@
       <c r="AH153" s="9"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="59"/>
+      <c r="A154" s="60"/>
       <c r="B154" s="9"/>
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
@@ -6647,7 +6655,7 @@
       <c r="AH154" s="9"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="59"/>
+      <c r="A155" s="60"/>
       <c r="B155" s="9"/>
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
@@ -6683,7 +6691,7 @@
       <c r="AH155" s="9"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="59"/>
+      <c r="A156" s="60"/>
       <c r="B156" s="9"/>
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
@@ -6719,7 +6727,7 @@
       <c r="AH156" s="9"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="59"/>
+      <c r="A157" s="60"/>
       <c r="B157" s="9"/>
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
@@ -6755,7 +6763,7 @@
       <c r="AH157" s="9"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="59"/>
+      <c r="A158" s="60"/>
       <c r="B158" s="9"/>
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
@@ -6791,7 +6799,7 @@
       <c r="AH158" s="9"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="59"/>
+      <c r="A159" s="60"/>
       <c r="B159" s="9"/>
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
@@ -6827,7 +6835,7 @@
       <c r="AH159" s="9"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="59"/>
+      <c r="A160" s="60"/>
       <c r="B160" s="9"/>
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
@@ -6863,7 +6871,7 @@
       <c r="AH160" s="9"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="59"/>
+      <c r="A161" s="60"/>
       <c r="B161" s="9"/>
       <c r="C161" s="9"/>
       <c r="D161" s="9"/>
@@ -6899,7 +6907,7 @@
       <c r="AH161" s="9"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="59"/>
+      <c r="A162" s="60"/>
       <c r="B162" s="9"/>
       <c r="C162" s="9"/>
       <c r="D162" s="9"/>
@@ -6935,7 +6943,7 @@
       <c r="AH162" s="9"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="59"/>
+      <c r="A163" s="60"/>
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
@@ -6971,7 +6979,7 @@
       <c r="AH163" s="9"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="59"/>
+      <c r="A164" s="60"/>
       <c r="B164" s="9"/>
       <c r="C164" s="9"/>
       <c r="D164" s="9"/>
@@ -7007,7 +7015,7 @@
       <c r="AH164" s="9"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="59"/>
+      <c r="A165" s="60"/>
       <c r="B165" s="9"/>
       <c r="C165" s="9"/>
       <c r="D165" s="9"/>
@@ -7043,7 +7051,7 @@
       <c r="AH165" s="9"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="59"/>
+      <c r="A166" s="60"/>
       <c r="B166" s="9"/>
       <c r="C166" s="9"/>
       <c r="D166" s="9"/>
@@ -7079,7 +7087,7 @@
       <c r="AH166" s="9"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="59"/>
+      <c r="A167" s="60"/>
       <c r="B167" s="9"/>
       <c r="C167" s="9"/>
       <c r="D167" s="9"/>
@@ -7115,7 +7123,7 @@
       <c r="AH167" s="9"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="59"/>
+      <c r="A168" s="60"/>
       <c r="B168" s="9"/>
       <c r="C168" s="9"/>
       <c r="D168" s="9"/>
@@ -7151,7 +7159,7 @@
       <c r="AH168" s="9"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="59"/>
+      <c r="A169" s="60"/>
       <c r="B169" s="9"/>
       <c r="C169" s="9"/>
       <c r="D169" s="9"/>
@@ -7187,7 +7195,7 @@
       <c r="AH169" s="9"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="59"/>
+      <c r="A170" s="60"/>
       <c r="B170" s="9"/>
       <c r="C170" s="9"/>
       <c r="D170" s="9"/>
@@ -7223,7 +7231,7 @@
       <c r="AH170" s="9"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="59"/>
+      <c r="A171" s="60"/>
       <c r="B171" s="9"/>
       <c r="C171" s="9"/>
       <c r="D171" s="9"/>
@@ -7259,7 +7267,7 @@
       <c r="AH171" s="9"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="59"/>
+      <c r="A172" s="60"/>
       <c r="B172" s="9"/>
       <c r="C172" s="9"/>
       <c r="D172" s="9"/>
@@ -7295,7 +7303,7 @@
       <c r="AH172" s="9"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="59"/>
+      <c r="A173" s="60"/>
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
       <c r="D173" s="9"/>
@@ -7331,7 +7339,7 @@
       <c r="AH173" s="9"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="59"/>
+      <c r="A174" s="60"/>
       <c r="B174" s="9"/>
       <c r="C174" s="9"/>
       <c r="D174" s="9"/>
@@ -7367,7 +7375,7 @@
       <c r="AH174" s="9"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="59"/>
+      <c r="A175" s="60"/>
       <c r="B175" s="9"/>
       <c r="C175" s="9"/>
       <c r="D175" s="9"/>
@@ -7403,7 +7411,7 @@
       <c r="AH175" s="9"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="59"/>
+      <c r="A176" s="60"/>
       <c r="B176" s="9"/>
       <c r="C176" s="9"/>
       <c r="D176" s="9"/>
@@ -7439,7 +7447,7 @@
       <c r="AH176" s="9"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="59"/>
+      <c r="A177" s="60"/>
       <c r="B177" s="9"/>
       <c r="C177" s="9"/>
       <c r="D177" s="9"/>
@@ -7475,7 +7483,7 @@
       <c r="AH177" s="9"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="59"/>
+      <c r="A178" s="60"/>
       <c r="B178" s="9"/>
       <c r="C178" s="9"/>
       <c r="D178" s="9"/>
@@ -7511,7 +7519,7 @@
       <c r="AH178" s="9"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="59"/>
+      <c r="A179" s="60"/>
       <c r="B179" s="9"/>
       <c r="C179" s="9"/>
       <c r="D179" s="9"/>
@@ -7547,7 +7555,7 @@
       <c r="AH179" s="9"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="59"/>
+      <c r="A180" s="60"/>
       <c r="B180" s="9"/>
       <c r="C180" s="9"/>
       <c r="D180" s="9"/>
@@ -7583,7 +7591,7 @@
       <c r="AH180" s="9"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="59"/>
+      <c r="A181" s="60"/>
       <c r="B181" s="9"/>
       <c r="C181" s="9"/>
       <c r="D181" s="9"/>
@@ -7619,7 +7627,7 @@
       <c r="AH181" s="9"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="59"/>
+      <c r="A182" s="60"/>
       <c r="B182" s="9"/>
       <c r="C182" s="9"/>
       <c r="D182" s="9"/>
@@ -7655,7 +7663,7 @@
       <c r="AH182" s="9"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="59"/>
+      <c r="A183" s="60"/>
       <c r="B183" s="9"/>
       <c r="C183" s="9"/>
       <c r="D183" s="9"/>
@@ -7691,7 +7699,7 @@
       <c r="AH183" s="9"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="59"/>
+      <c r="A184" s="60"/>
       <c r="B184" s="9"/>
       <c r="C184" s="9"/>
       <c r="D184" s="9"/>
@@ -7727,7 +7735,7 @@
       <c r="AH184" s="9"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="59"/>
+      <c r="A185" s="60"/>
       <c r="B185" s="9"/>
       <c r="C185" s="9"/>
       <c r="D185" s="9"/>
@@ -7763,7 +7771,7 @@
       <c r="AH185" s="9"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="59"/>
+      <c r="A186" s="60"/>
       <c r="B186" s="9"/>
       <c r="C186" s="9"/>
       <c r="D186" s="9"/>
@@ -7799,7 +7807,7 @@
       <c r="AH186" s="9"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="59"/>
+      <c r="A187" s="60"/>
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
       <c r="D187" s="9"/>
@@ -7835,7 +7843,7 @@
       <c r="AH187" s="9"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="59"/>
+      <c r="A188" s="60"/>
       <c r="B188" s="9"/>
       <c r="C188" s="9"/>
       <c r="D188" s="9"/>
@@ -7871,7 +7879,7 @@
       <c r="AH188" s="9"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="59"/>
+      <c r="A189" s="60"/>
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
       <c r="D189" s="9"/>
@@ -7907,7 +7915,7 @@
       <c r="AH189" s="9"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="59"/>
+      <c r="A190" s="60"/>
       <c r="B190" s="9"/>
       <c r="C190" s="9"/>
       <c r="D190" s="9"/>
@@ -7943,7 +7951,7 @@
       <c r="AH190" s="9"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="59"/>
+      <c r="A191" s="60"/>
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
       <c r="D191" s="9"/>
@@ -7979,7 +7987,7 @@
       <c r="AH191" s="9"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="59"/>
+      <c r="A192" s="60"/>
       <c r="B192" s="9"/>
       <c r="C192" s="9"/>
       <c r="D192" s="9"/>
@@ -8015,7 +8023,7 @@
       <c r="AH192" s="9"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="59"/>
+      <c r="A193" s="60"/>
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
       <c r="D193" s="9"/>
@@ -8051,7 +8059,7 @@
       <c r="AH193" s="9"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="59"/>
+      <c r="A194" s="60"/>
       <c r="B194" s="9"/>
       <c r="C194" s="9"/>
       <c r="D194" s="9"/>
@@ -8087,7 +8095,7 @@
       <c r="AH194" s="9"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="59"/>
+      <c r="A195" s="60"/>
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
       <c r="D195" s="9"/>
@@ -8123,7 +8131,7 @@
       <c r="AH195" s="9"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="59"/>
+      <c r="A196" s="60"/>
       <c r="B196" s="9"/>
       <c r="C196" s="9"/>
       <c r="D196" s="9"/>
@@ -8159,7 +8167,7 @@
       <c r="AH196" s="9"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="59"/>
+      <c r="A197" s="60"/>
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
       <c r="D197" s="9"/>
@@ -8195,7 +8203,7 @@
       <c r="AH197" s="9"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="59"/>
+      <c r="A198" s="60"/>
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
       <c r="D198" s="9"/>
@@ -8231,7 +8239,7 @@
       <c r="AH198" s="9"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="59"/>
+      <c r="A199" s="60"/>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
       <c r="D199" s="9"/>
@@ -8267,7 +8275,7 @@
       <c r="AH199" s="9"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="59"/>
+      <c r="A200" s="60"/>
       <c r="B200" s="9"/>
       <c r="C200" s="9"/>
       <c r="D200" s="9"/>
@@ -8303,7 +8311,7 @@
       <c r="AH200" s="9"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="59"/>
+      <c r="A201" s="60"/>
       <c r="B201" s="9"/>
       <c r="C201" s="9"/>
       <c r="D201" s="9"/>
@@ -8339,7 +8347,7 @@
       <c r="AH201" s="9"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="59"/>
+      <c r="A202" s="60"/>
       <c r="B202" s="9"/>
       <c r="C202" s="9"/>
       <c r="D202" s="9"/>
@@ -8375,7 +8383,7 @@
       <c r="AH202" s="9"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="59"/>
+      <c r="A203" s="60"/>
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
       <c r="D203" s="9"/>
@@ -8411,7 +8419,7 @@
       <c r="AH203" s="9"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="59"/>
+      <c r="A204" s="60"/>
       <c r="B204" s="9"/>
       <c r="C204" s="9"/>
       <c r="D204" s="9"/>
@@ -8447,7 +8455,7 @@
       <c r="AH204" s="9"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="59"/>
+      <c r="A205" s="60"/>
       <c r="B205" s="9"/>
       <c r="C205" s="9"/>
       <c r="D205" s="9"/>
@@ -8483,7 +8491,7 @@
       <c r="AH205" s="9"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="59"/>
+      <c r="A206" s="60"/>
       <c r="B206" s="9"/>
       <c r="C206" s="9"/>
       <c r="D206" s="9"/>
@@ -8519,7 +8527,7 @@
       <c r="AH206" s="9"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="59"/>
+      <c r="A207" s="60"/>
       <c r="B207" s="9"/>
       <c r="C207" s="9"/>
       <c r="D207" s="9"/>
@@ -8555,7 +8563,7 @@
       <c r="AH207" s="9"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="59"/>
+      <c r="A208" s="60"/>
       <c r="B208" s="9"/>
       <c r="C208" s="9"/>
       <c r="D208" s="9"/>
@@ -8591,7 +8599,7 @@
       <c r="AH208" s="9"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="59"/>
+      <c r="A209" s="60"/>
       <c r="B209" s="9"/>
       <c r="C209" s="9"/>
       <c r="D209" s="9"/>
@@ -8627,7 +8635,7 @@
       <c r="AH209" s="9"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="59"/>
+      <c r="A210" s="60"/>
       <c r="B210" s="9"/>
       <c r="C210" s="9"/>
       <c r="D210" s="9"/>
@@ -8663,7 +8671,7 @@
       <c r="AH210" s="9"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="59"/>
+      <c r="A211" s="60"/>
       <c r="B211" s="9"/>
       <c r="C211" s="9"/>
       <c r="D211" s="9"/>
@@ -8699,7 +8707,7 @@
       <c r="AH211" s="9"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="59"/>
+      <c r="A212" s="60"/>
       <c r="B212" s="9"/>
       <c r="C212" s="9"/>
       <c r="D212" s="9"/>
@@ -8735,7 +8743,7 @@
       <c r="AH212" s="9"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="59"/>
+      <c r="A213" s="60"/>
       <c r="B213" s="9"/>
       <c r="C213" s="9"/>
       <c r="D213" s="9"/>
@@ -8771,7 +8779,7 @@
       <c r="AH213" s="9"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="59"/>
+      <c r="A214" s="60"/>
       <c r="B214" s="9"/>
       <c r="C214" s="9"/>
       <c r="D214" s="9"/>
@@ -8807,7 +8815,7 @@
       <c r="AH214" s="9"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="59"/>
+      <c r="A215" s="60"/>
       <c r="B215" s="9"/>
       <c r="C215" s="9"/>
       <c r="D215" s="9"/>
@@ -8843,7 +8851,7 @@
       <c r="AH215" s="9"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="59"/>
+      <c r="A216" s="60"/>
       <c r="B216" s="9"/>
       <c r="C216" s="9"/>
       <c r="D216" s="9"/>
@@ -8879,7 +8887,7 @@
       <c r="AH216" s="9"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="59"/>
+      <c r="A217" s="60"/>
       <c r="B217" s="9"/>
       <c r="C217" s="9"/>
       <c r="D217" s="9"/>
@@ -8915,7 +8923,7 @@
       <c r="AH217" s="9"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="59"/>
+      <c r="A218" s="60"/>
       <c r="B218" s="9"/>
       <c r="C218" s="9"/>
       <c r="D218" s="9"/>
@@ -8951,7 +8959,7 @@
       <c r="AH218" s="9"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="59"/>
+      <c r="A219" s="60"/>
       <c r="B219" s="9"/>
       <c r="C219" s="9"/>
       <c r="D219" s="9"/>
@@ -8987,7 +8995,7 @@
       <c r="AH219" s="9"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="59"/>
+      <c r="A220" s="60"/>
       <c r="B220" s="9"/>
       <c r="C220" s="9"/>
       <c r="D220" s="9"/>
@@ -9023,7 +9031,7 @@
       <c r="AH220" s="9"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="59"/>
+      <c r="A221" s="60"/>
       <c r="B221" s="9"/>
       <c r="C221" s="9"/>
       <c r="D221" s="9"/>
@@ -9059,7 +9067,7 @@
       <c r="AH221" s="9"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="59"/>
+      <c r="A222" s="60"/>
       <c r="B222" s="9"/>
       <c r="C222" s="9"/>
       <c r="D222" s="9"/>
@@ -9095,7 +9103,7 @@
       <c r="AH222" s="9"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="59"/>
+      <c r="A223" s="60"/>
       <c r="B223" s="9"/>
       <c r="C223" s="9"/>
       <c r="D223" s="9"/>
@@ -9131,7 +9139,7 @@
       <c r="AH223" s="9"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="59"/>
+      <c r="A224" s="60"/>
       <c r="B224" s="9"/>
       <c r="C224" s="9"/>
       <c r="D224" s="9"/>
@@ -9167,7 +9175,7 @@
       <c r="AH224" s="9"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="59"/>
+      <c r="A225" s="60"/>
       <c r="B225" s="9"/>
       <c r="C225" s="9"/>
       <c r="D225" s="9"/>
@@ -9203,7 +9211,7 @@
       <c r="AH225" s="9"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="59"/>
+      <c r="A226" s="60"/>
       <c r="B226" s="9"/>
       <c r="C226" s="9"/>
       <c r="D226" s="9"/>
@@ -9239,7 +9247,7 @@
       <c r="AH226" s="9"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="59"/>
+      <c r="A227" s="60"/>
       <c r="B227" s="9"/>
       <c r="C227" s="9"/>
       <c r="D227" s="9"/>
@@ -9275,7 +9283,7 @@
       <c r="AH227" s="9"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="59"/>
+      <c r="A228" s="60"/>
       <c r="B228" s="9"/>
       <c r="C228" s="9"/>
       <c r="D228" s="9"/>
@@ -9311,7 +9319,7 @@
       <c r="AH228" s="9"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="59"/>
+      <c r="A229" s="60"/>
       <c r="B229" s="9"/>
       <c r="C229" s="9"/>
       <c r="D229" s="9"/>
@@ -9347,7 +9355,7 @@
       <c r="AH229" s="9"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="59"/>
+      <c r="A230" s="60"/>
       <c r="B230" s="9"/>
       <c r="C230" s="9"/>
       <c r="D230" s="9"/>
@@ -9383,7 +9391,7 @@
       <c r="AH230" s="9"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="59"/>
+      <c r="A231" s="60"/>
       <c r="B231" s="9"/>
       <c r="C231" s="9"/>
       <c r="D231" s="9"/>
@@ -9419,7 +9427,7 @@
       <c r="AH231" s="9"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="59"/>
+      <c r="A232" s="60"/>
       <c r="B232" s="9"/>
       <c r="C232" s="9"/>
       <c r="D232" s="9"/>
@@ -9455,7 +9463,7 @@
       <c r="AH232" s="9"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="59"/>
+      <c r="A233" s="60"/>
       <c r="B233" s="9"/>
       <c r="C233" s="9"/>
       <c r="D233" s="9"/>
@@ -9491,7 +9499,7 @@
       <c r="AH233" s="9"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="59"/>
+      <c r="A234" s="60"/>
       <c r="B234" s="9"/>
       <c r="C234" s="9"/>
       <c r="D234" s="9"/>
@@ -9527,7 +9535,7 @@
       <c r="AH234" s="9"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="59"/>
+      <c r="A235" s="60"/>
       <c r="B235" s="9"/>
       <c r="C235" s="9"/>
       <c r="D235" s="9"/>
@@ -9563,7 +9571,7 @@
       <c r="AH235" s="9"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="59"/>
+      <c r="A236" s="60"/>
       <c r="B236" s="9"/>
       <c r="C236" s="9"/>
       <c r="D236" s="9"/>
@@ -9599,7 +9607,7 @@
       <c r="AH236" s="9"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="59"/>
+      <c r="A237" s="60"/>
       <c r="B237" s="9"/>
       <c r="C237" s="9"/>
       <c r="D237" s="9"/>
@@ -9635,7 +9643,7 @@
       <c r="AH237" s="9"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="59"/>
+      <c r="A238" s="60"/>
       <c r="B238" s="9"/>
       <c r="C238" s="9"/>
       <c r="D238" s="9"/>
@@ -9671,7 +9679,7 @@
       <c r="AH238" s="9"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="59"/>
+      <c r="A239" s="60"/>
       <c r="B239" s="9"/>
       <c r="C239" s="9"/>
       <c r="D239" s="9"/>
@@ -9707,7 +9715,7 @@
       <c r="AH239" s="9"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="59"/>
+      <c r="A240" s="60"/>
       <c r="B240" s="9"/>
       <c r="C240" s="9"/>
       <c r="D240" s="9"/>
@@ -9743,7 +9751,7 @@
       <c r="AH240" s="9"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="59"/>
+      <c r="A241" s="60"/>
       <c r="B241" s="9"/>
       <c r="C241" s="9"/>
       <c r="D241" s="9"/>
@@ -9779,7 +9787,7 @@
       <c r="AH241" s="9"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="59"/>
+      <c r="A242" s="60"/>
       <c r="B242" s="9"/>
       <c r="C242" s="9"/>
       <c r="D242" s="9"/>
@@ -9815,7 +9823,7 @@
       <c r="AH242" s="9"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="59"/>
+      <c r="A243" s="60"/>
       <c r="B243" s="9"/>
       <c r="C243" s="9"/>
       <c r="D243" s="9"/>
@@ -9851,7 +9859,7 @@
       <c r="AH243" s="9"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="59"/>
+      <c r="A244" s="60"/>
       <c r="B244" s="9"/>
       <c r="C244" s="9"/>
       <c r="D244" s="9"/>
@@ -9887,7 +9895,7 @@
       <c r="AH244" s="9"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="59"/>
+      <c r="A245" s="60"/>
       <c r="B245" s="9"/>
       <c r="C245" s="9"/>
       <c r="D245" s="9"/>
@@ -9923,7 +9931,7 @@
       <c r="AH245" s="9"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="59"/>
+      <c r="A246" s="60"/>
       <c r="B246" s="9"/>
       <c r="C246" s="9"/>
       <c r="D246" s="9"/>
@@ -9959,7 +9967,7 @@
       <c r="AH246" s="9"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="59"/>
+      <c r="A247" s="60"/>
       <c r="B247" s="9"/>
       <c r="C247" s="9"/>
       <c r="D247" s="9"/>
@@ -9995,7 +10003,7 @@
       <c r="AH247" s="9"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="59"/>
+      <c r="A248" s="60"/>
       <c r="B248" s="9"/>
       <c r="C248" s="9"/>
       <c r="D248" s="9"/>
@@ -10031,7 +10039,7 @@
       <c r="AH248" s="9"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="59"/>
+      <c r="A249" s="60"/>
       <c r="B249" s="9"/>
       <c r="C249" s="9"/>
       <c r="D249" s="9"/>
@@ -10067,7 +10075,7 @@
       <c r="AH249" s="9"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="59"/>
+      <c r="A250" s="60"/>
       <c r="B250" s="9"/>
       <c r="C250" s="9"/>
       <c r="D250" s="9"/>
@@ -10103,7 +10111,7 @@
       <c r="AH250" s="9"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="59"/>
+      <c r="A251" s="60"/>
       <c r="B251" s="9"/>
       <c r="C251" s="9"/>
       <c r="D251" s="9"/>
@@ -10139,7 +10147,7 @@
       <c r="AH251" s="9"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="59"/>
+      <c r="A252" s="60"/>
       <c r="B252" s="9"/>
       <c r="C252" s="9"/>
       <c r="D252" s="9"/>
@@ -10175,7 +10183,7 @@
       <c r="AH252" s="9"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="59"/>
+      <c r="A253" s="60"/>
       <c r="B253" s="9"/>
       <c r="C253" s="9"/>
       <c r="D253" s="9"/>
@@ -10211,7 +10219,7 @@
       <c r="AH253" s="9"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="59"/>
+      <c r="A254" s="60"/>
       <c r="B254" s="9"/>
       <c r="C254" s="9"/>
       <c r="D254" s="9"/>
@@ -10247,7 +10255,7 @@
       <c r="AH254" s="9"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="59"/>
+      <c r="A255" s="60"/>
       <c r="B255" s="9"/>
       <c r="C255" s="9"/>
       <c r="D255" s="9"/>
@@ -10283,7 +10291,7 @@
       <c r="AH255" s="9"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="59"/>
+      <c r="A256" s="60"/>
       <c r="B256" s="9"/>
       <c r="C256" s="9"/>
       <c r="D256" s="9"/>
@@ -10319,7 +10327,7 @@
       <c r="AH256" s="9"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="59"/>
+      <c r="A257" s="60"/>
       <c r="B257" s="9"/>
       <c r="C257" s="9"/>
       <c r="D257" s="9"/>
@@ -10355,7 +10363,7 @@
       <c r="AH257" s="9"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="59"/>
+      <c r="A258" s="60"/>
       <c r="B258" s="9"/>
       <c r="C258" s="9"/>
       <c r="D258" s="9"/>
@@ -10391,7 +10399,7 @@
       <c r="AH258" s="9"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="59"/>
+      <c r="A259" s="60"/>
       <c r="B259" s="9"/>
       <c r="C259" s="9"/>
       <c r="D259" s="9"/>
@@ -10427,7 +10435,7 @@
       <c r="AH259" s="9"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="59"/>
+      <c r="A260" s="60"/>
       <c r="B260" s="9"/>
       <c r="C260" s="9"/>
       <c r="D260" s="9"/>
@@ -10463,7 +10471,7 @@
       <c r="AH260" s="9"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="59"/>
+      <c r="A261" s="60"/>
       <c r="B261" s="9"/>
       <c r="C261" s="9"/>
       <c r="D261" s="9"/>
@@ -10499,7 +10507,7 @@
       <c r="AH261" s="9"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="59"/>
+      <c r="A262" s="60"/>
       <c r="B262" s="9"/>
       <c r="C262" s="9"/>
       <c r="D262" s="9"/>
@@ -11273,7 +11281,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="339">
+  <mergeCells count="353">
     <mergeCell ref="H13:H17"/>
     <mergeCell ref="I13:I17"/>
     <mergeCell ref="J13:J17"/>
@@ -11409,6 +11417,17 @@
     <mergeCell ref="F92:F95"/>
     <mergeCell ref="G92:G95"/>
     <mergeCell ref="H92:H95"/>
+    <mergeCell ref="L96:L97"/>
+    <mergeCell ref="M96:M97"/>
+    <mergeCell ref="N96:N97"/>
+    <mergeCell ref="O96:O97"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="E96:E97"/>
+    <mergeCell ref="J96:J97"/>
+    <mergeCell ref="K96:K97"/>
     <mergeCell ref="H71:H73"/>
     <mergeCell ref="I71:I73"/>
     <mergeCell ref="J71:J73"/>
@@ -11448,17 +11467,20 @@
     <mergeCell ref="I77:I79"/>
     <mergeCell ref="J77:J79"/>
     <mergeCell ref="K77:K79"/>
-    <mergeCell ref="L96:L97"/>
-    <mergeCell ref="M96:M97"/>
-    <mergeCell ref="N96:N97"/>
-    <mergeCell ref="O96:O97"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="E96:E97"/>
-    <mergeCell ref="J96:J97"/>
-    <mergeCell ref="K96:K97"/>
+    <mergeCell ref="I98:I100"/>
+    <mergeCell ref="J98:J100"/>
+    <mergeCell ref="K98:K100"/>
+    <mergeCell ref="L98:L100"/>
+    <mergeCell ref="M98:M100"/>
+    <mergeCell ref="N98:N100"/>
+    <mergeCell ref="O98:O100"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="C98:C100"/>
+    <mergeCell ref="E98:E100"/>
+    <mergeCell ref="F98:F100"/>
+    <mergeCell ref="G98:G100"/>
+    <mergeCell ref="H98:H100"/>
     <mergeCell ref="H22:H26"/>
     <mergeCell ref="I22:I26"/>
     <mergeCell ref="J22:J26"/>
@@ -11636,58 +11658,58 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="B2" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="60" t="s">
-        <v>146</v>
+      <c r="A2" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="61" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="60" t="s">
-        <v>147</v>
-      </c>
-      <c r="B3" s="60" t="s">
-        <v>148</v>
-      </c>
-      <c r="C3" s="60" t="s">
-        <v>149</v>
+      <c r="A3" s="61" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="61" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="B4" s="60" t="s">
+      <c r="A4" s="61" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="60" t="s">
-        <v>151</v>
+      <c r="C4" s="61" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="B5" s="60" t="s">
-        <v>153</v>
-      </c>
-      <c r="C5" s="60" t="s">
-        <v>154</v>
+      <c r="A5" s="61" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="60" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="C6" s="60" t="s">
-        <v>157</v>
+      <c r="A6" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="61" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1"/>

--- a/Grade2-Homeworks.xlsx
+++ b/Grade2-Homeworks.xlsx
@@ -700,21 +700,7 @@
     <t>HW: Complete previous HWs</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <strike/>
-        <color theme="1"/>
-      </rPr>
-      <t>- HW: Fix MD file and complete exercises (Combined proportions - AI notes - exercises)</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve"> - Student needs help</t>
-    </r>
+    <t xml:space="preserve">- HW: Fix MD file and complete exercises (Combined proportions - AI notes - exercises) </t>
   </si>
   <si>
     <t>HW: Complete these exercises(AI exercises on stories)</t>
@@ -37227,12 +37213,12 @@
     <mergeCell ref="G30:G33"/>
     <mergeCell ref="H34:H37"/>
     <mergeCell ref="I34:I37"/>
+    <mergeCell ref="J34:J35"/>
     <mergeCell ref="K34:K37"/>
     <mergeCell ref="L34:L37"/>
     <mergeCell ref="M34:M37"/>
     <mergeCell ref="N34:N37"/>
     <mergeCell ref="O34:O37"/>
-    <mergeCell ref="J34:J35"/>
     <mergeCell ref="A34:A37"/>
     <mergeCell ref="B34:B37"/>
     <mergeCell ref="C34:C37"/>
